--- a/output/Morgan_Recap_Data_Tape.xlsx
+++ b/output/Morgan_Recap_Data_Tape.xlsx
@@ -9,10 +9,12 @@
   <sheets>
     <sheet name="Portfolio Data Tape" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Calc" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="» Operating T12 (monthly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="» Rent &amp; Leasing" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="» Underwriting &amp; Returns" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="» Demographics" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="» NOI Bridge (T12 vs JLL)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="» Operating T12 (monthly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="» Rent &amp; Leasing" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="» Unit Mix (by plan)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="» Underwriting &amp; Returns" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="» Demographics" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -999,7 +1001,7 @@
       </c>
       <c r="M16" s="18" t="inlineStr">
         <is>
-          <t>JLL Cap</t>
+          <t>In-Place Cap</t>
         </is>
       </c>
       <c r="N16" s="18" t="inlineStr">
@@ -1052,7 +1054,7 @@
         <v>0.9694989106753813</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>2305.485781990521</v>
+        <v>2295.846846846847</v>
       </c>
       <c r="J17" s="25" t="n">
         <v>0.03463420147578833</v>
@@ -1103,7 +1105,7 @@
         <v>0.923728813559322</v>
       </c>
       <c r="I18" s="33" t="n">
-        <v>2491.679611650486</v>
+        <v>2499.940366972477</v>
       </c>
       <c r="J18" s="34" t="n">
         <v>-0.115485050906139</v>
@@ -1154,7 +1156,7 @@
         <v>0.937888198757764</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>1589.922535211268</v>
+        <v>1603</v>
       </c>
       <c r="J19" s="25" t="n">
         <v>-0.1521936575618804</v>
@@ -1205,7 +1207,7 @@
         <v>0.9488372093023256</v>
       </c>
       <c r="I20" s="33" t="n">
-        <v>1883.005128205128</v>
+        <v>1889.813725490196</v>
       </c>
       <c r="J20" s="34" t="n">
         <v>-0.07013679161485165</v>
@@ -1973,6 +1975,364 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:R5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="B1" s="17" t="inlineStr">
+        <is>
+          <t>GPR (T12)</t>
+        </is>
+      </c>
+      <c r="C1" s="17" t="inlineStr">
+        <is>
+          <t>GPR (JLL Yr0)</t>
+        </is>
+      </c>
+      <c r="D1" s="17" t="inlineStr">
+        <is>
+          <t>EGR (T12)</t>
+        </is>
+      </c>
+      <c r="E1" s="17" t="inlineStr">
+        <is>
+          <t>EGR (JLL Yr0)</t>
+        </is>
+      </c>
+      <c r="F1" s="17" t="inlineStr">
+        <is>
+          <t>Opex (T12)</t>
+        </is>
+      </c>
+      <c r="G1" s="17" t="inlineStr">
+        <is>
+          <t>Opex (JLL Yr0)</t>
+        </is>
+      </c>
+      <c r="H1" s="17" t="inlineStr">
+        <is>
+          <t>RE Taxes (T12 actual)</t>
+        </is>
+      </c>
+      <c r="I1" s="17" t="inlineStr">
+        <is>
+          <t>RE Taxes (JLL UW)</t>
+        </is>
+      </c>
+      <c r="J1" s="17" t="inlineStr">
+        <is>
+          <t>Tax Adjustment</t>
+        </is>
+      </c>
+      <c r="K1" s="17" t="inlineStr">
+        <is>
+          <t>Current Assessment</t>
+        </is>
+      </c>
+      <c r="L1" s="17" t="inlineStr">
+        <is>
+          <t>Purchase Basis</t>
+        </is>
+      </c>
+      <c r="M1" s="17" t="inlineStr">
+        <is>
+          <t>NOI (T12)</t>
+        </is>
+      </c>
+      <c r="N1" s="17" t="inlineStr">
+        <is>
+          <t>NOI (T3 ann)</t>
+        </is>
+      </c>
+      <c r="O1" s="17" t="inlineStr">
+        <is>
+          <t>NOI (JLL Yr0)</t>
+        </is>
+      </c>
+      <c r="P1" s="17" t="inlineStr">
+        <is>
+          <t>Trailing Cap</t>
+        </is>
+      </c>
+      <c r="Q1" s="17" t="inlineStr">
+        <is>
+          <t>In-Place Cap (JLL)</t>
+        </is>
+      </c>
+      <c r="R1" s="17" t="inlineStr">
+        <is>
+          <t>NOI UW vs Trailing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>13029128</v>
+      </c>
+      <c r="C2" t="n">
+        <v>13027512</v>
+      </c>
+      <c r="D2" t="n">
+        <v>13094818</v>
+      </c>
+      <c r="E2" t="n">
+        <v>13287470</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6538581</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6848482</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2446542</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2737885</v>
+      </c>
+      <c r="J2" t="n">
+        <v>291343</v>
+      </c>
+      <c r="K2" t="n">
+        <v>127743502</v>
+      </c>
+      <c r="L2" t="n">
+        <v>127000000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>6556237</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6795024</v>
+      </c>
+      <c r="O2" t="n">
+        <v>6438989</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.0516</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.0507</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-0.0179</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Caroline Golden Glades</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7184412</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7184412</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6664600</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6946619</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2862204</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2980455</v>
+      </c>
+      <c r="H3" t="n">
+        <v>966874</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1151356</v>
+      </c>
+      <c r="J3" t="n">
+        <v>184482</v>
+      </c>
+      <c r="K3" t="n">
+        <v>51500000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>85000000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3802396</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4008968</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3966164</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.0447</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.0467</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0431</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>6998364</v>
+      </c>
+      <c r="C4" t="n">
+        <v>6998364</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6704527</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6759018</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3931707</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3680950</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1343307</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1255417</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-87890</v>
+      </c>
+      <c r="K4" t="n">
+        <v>64391737</v>
+      </c>
+      <c r="L4" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2772820</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2723864</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3078068</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.0462</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.1101</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5033880</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5033880</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5119221</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5141418</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2878929</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2828366</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1019356</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1034561</v>
+      </c>
+      <c r="J5" t="n">
+        <v>15205</v>
+      </c>
+      <c r="K5" t="n">
+        <v>46814087</v>
+      </c>
+      <c r="L5" t="n">
+        <v>46500000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2240292</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2105752</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2313052</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.0497</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.0325</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3173,7 +3533,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3286,7 +3646,7 @@
         <v>0.9913</v>
       </c>
       <c r="E2" t="n">
-        <v>2305</v>
+        <v>2296</v>
       </c>
       <c r="F2" t="n">
         <v>2.02</v>
@@ -3332,10 +3692,10 @@
         <v>0.9915</v>
       </c>
       <c r="E3" t="n">
-        <v>2492</v>
+        <v>2500</v>
       </c>
       <c r="F3" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0021</v>
@@ -3378,10 +3738,10 @@
         <v>0.9969</v>
       </c>
       <c r="E4" t="n">
-        <v>1590</v>
+        <v>1603</v>
       </c>
       <c r="F4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0266</v>
@@ -3424,7 +3784,7 @@
         <v>0.9953</v>
       </c>
       <c r="E5" t="n">
-        <v>1883</v>
+        <v>1890</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -3459,7 +3819,5143 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q89"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="B1" s="17" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C1" s="17" t="inlineStr">
+        <is>
+          <t>Bed</t>
+        </is>
+      </c>
+      <c r="D1" s="17" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="E1" s="17" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="F1" s="17" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="G1" s="17" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="H1" s="17" t="inlineStr">
+        <is>
+          <t>Avg SF</t>
+        </is>
+      </c>
+      <c r="I1" s="17" t="inlineStr">
+        <is>
+          <t>In-Place</t>
+        </is>
+      </c>
+      <c r="J1" s="17" t="inlineStr">
+        <is>
+          <t>HD90 Ask</t>
+        </is>
+      </c>
+      <c r="K1" s="17" t="inlineStr">
+        <is>
+          <t>HD90 Eff</t>
+        </is>
+      </c>
+      <c r="L1" s="17" t="inlineStr">
+        <is>
+          <t>HD365 Ask</t>
+        </is>
+      </c>
+      <c r="M1" s="17" t="inlineStr">
+        <is>
+          <t>HD365 Eff</t>
+        </is>
+      </c>
+      <c r="N1" s="17" t="inlineStr">
+        <is>
+          <t>New Leases</t>
+        </is>
+      </c>
+      <c r="O1" s="17" t="inlineStr">
+        <is>
+          <t>Renewals</t>
+        </is>
+      </c>
+      <c r="P1" s="17" t="inlineStr">
+        <is>
+          <t>Last5 New Avg</t>
+        </is>
+      </c>
+      <c r="Q1" s="17" t="inlineStr">
+        <is>
+          <t>HD Ask YoY</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A0</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2" t="n">
+        <v>19</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>657</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1478</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1540</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1495</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1481</v>
+      </c>
+      <c r="N2" t="n">
+        <v>7</v>
+      </c>
+      <c r="O2" t="n">
+        <v>14</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1427</v>
+      </c>
+      <c r="Q2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>71</v>
+      </c>
+      <c r="F3" t="n">
+        <v>63</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>704</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1559</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1774</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1774</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1662</v>
+      </c>
+      <c r="N3" t="n">
+        <v>26</v>
+      </c>
+      <c r="O3" t="n">
+        <v>42</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1588</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.0293</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A1.1</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>754</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1638</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1740</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1740</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1646</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1616</v>
+      </c>
+      <c r="N4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O4" t="n">
+        <v>10</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1652</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.0968</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A1.2</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>776</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1709</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1774</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1774</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1662</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>10</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1626</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.0293</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A1.3</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>14</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>739</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1646</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1774</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1774</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1662</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>10</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1606</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.0293</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>21</v>
+      </c>
+      <c r="F7" t="n">
+        <v>19</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>887</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1736</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1781</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1781</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1786</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1752</v>
+      </c>
+      <c r="N7" t="n">
+        <v>11</v>
+      </c>
+      <c r="O7" t="n">
+        <v>10</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1695</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.0399</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>42</v>
+      </c>
+      <c r="F8" t="n">
+        <v>37</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1092</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2054</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2438</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2438</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2096</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2085</v>
+      </c>
+      <c r="N8" t="n">
+        <v>21</v>
+      </c>
+      <c r="O8" t="n">
+        <v>19</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2105</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1185</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A2.1</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>822</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1827</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1847</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1847</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1780</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1766</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>7</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1625</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.0833</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A2.1a</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>896</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1706</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2438</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2438</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2096</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2085</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1706</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.1185</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A2.3</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>11</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>904</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1761</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2438</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2438</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1850</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1821</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>7</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1779</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.1185</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1121</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2058</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2030</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2030</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2023</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2011</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2165</v>
+      </c>
+      <c r="Q12" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>948</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2001</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2074</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2074</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1979</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1969</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1970</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.07240000000000001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1021</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2415</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2290</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2290</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2290</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2290</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2415</v>
+      </c>
+      <c r="Q14" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>31</v>
+      </c>
+      <c r="F15" t="n">
+        <v>29</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1082</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1984</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2052</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2052</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2022</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2010</v>
+      </c>
+      <c r="N15" t="n">
+        <v>12</v>
+      </c>
+      <c r="O15" t="n">
+        <v>17</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2010</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.048</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A6.1</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1022</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2084</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2052</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2052</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2011</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2011</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.048</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>26</v>
+      </c>
+      <c r="F17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1569</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2928</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2452</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2452</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2767</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2758</v>
+      </c>
+      <c r="N17" t="n">
+        <v>13</v>
+      </c>
+      <c r="O17" t="n">
+        <v>13</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2921</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.2744</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>24</v>
+      </c>
+      <c r="F18" t="n">
+        <v>24</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1511</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3151</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2673</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2667</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2703</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2694</v>
+      </c>
+      <c r="N18" t="n">
+        <v>10</v>
+      </c>
+      <c r="O18" t="n">
+        <v>14</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3090</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.0025</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>34</v>
+      </c>
+      <c r="F19" t="n">
+        <v>33</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1296</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2698</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2497</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2497</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2520</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2511</v>
+      </c>
+      <c r="N19" t="n">
+        <v>13</v>
+      </c>
+      <c r="O19" t="n">
+        <v>20</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2707</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.0653</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>B4a</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1278</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2350</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2497</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2497</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2520</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2511</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2422</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.0653</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>B4b</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1330</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2366</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2497</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2497</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2520</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2511</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2302</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.0653</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>40</v>
+      </c>
+      <c r="F22" t="n">
+        <v>37</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1485</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2848</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3158</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3158</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2599</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2592</v>
+      </c>
+      <c r="N22" t="n">
+        <v>10</v>
+      </c>
+      <c r="O22" t="n">
+        <v>29</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2927</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.1064</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1637</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3549</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3829</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3829</v>
+      </c>
+      <c r="L23" t="n">
+        <v>3789</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3789</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3</v>
+      </c>
+      <c r="P23" t="n">
+        <v>3554</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.3682</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F24" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1995</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4030</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2620</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2620</v>
+      </c>
+      <c r="L24" t="n">
+        <v>3028</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3024</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O24" t="n">
+        <v>7</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3960</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.2286</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>12</v>
+      </c>
+      <c r="F25" t="n">
+        <v>12</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2256</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5036</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3387</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3387</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2848</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2836</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4</v>
+      </c>
+      <c r="O25" t="n">
+        <v>8</v>
+      </c>
+      <c r="P25" t="n">
+        <v>4902</v>
+      </c>
+      <c r="Q25" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>City Centre + Residences</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1866</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3516</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1860</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1860</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2672</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2662</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>6</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3414</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.4407</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Caroline Golden Glades</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>32</v>
+      </c>
+      <c r="F27" t="n">
+        <v>28</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>585</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1862</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1826</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1678</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1828</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1709</v>
+      </c>
+      <c r="N27" t="n">
+        <v>12</v>
+      </c>
+      <c r="O27" t="n">
+        <v>18</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1749</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-0.1104</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Caroline Golden Glades</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ST.WFH</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>585</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1953</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2032</v>
+      </c>
+      <c r="Q28" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Caroline Golden Glades</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>72</v>
+      </c>
+      <c r="F29" t="n">
+        <v>62</v>
+      </c>
+      <c r="G29" t="n">
+        <v>9</v>
+      </c>
+      <c r="H29" t="n">
+        <v>768</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2249</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2153</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2023</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2208</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2057</v>
+      </c>
+      <c r="N29" t="n">
+        <v>27</v>
+      </c>
+      <c r="O29" t="n">
+        <v>39</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2132</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-0.0949</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Caroline Golden Glades</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>A1.WFH</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" t="n">
+        <v>7</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>768</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2245</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2153</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2023</v>
+      </c>
+      <c r="L30" t="n">
+        <v>2160</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2006</v>
+      </c>
+      <c r="N30" t="n">
+        <v>7</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2194</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-0.0917</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Caroline Golden Glades</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>A1M</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>16</v>
+      </c>
+      <c r="F31" t="n">
+        <v>16</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>790</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2356</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2300</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2300</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2333</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2220</v>
+      </c>
+      <c r="N31" t="n">
+        <v>8</v>
+      </c>
+      <c r="O31" t="n">
+        <v>8</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2231</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>-0.08799999999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Caroline Golden Glades</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A1M.WFH</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>790</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2267</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2104</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1929</v>
+      </c>
+      <c r="L32" t="n">
+        <v>2169</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1996</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>-0.1153</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Caroline Golden Glades</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>767</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2408</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>2302</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2110</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2411</v>
+      </c>
+      <c r="Q33" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Caroline Golden Glades</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16</v>
+      </c>
+      <c r="F34" t="n">
+        <v>14</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1071</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2805</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2928</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2716</v>
+      </c>
+      <c r="L34" t="n">
+        <v>2809</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2508</v>
+      </c>
+      <c r="N34" t="n">
+        <v>9</v>
+      </c>
+      <c r="O34" t="n">
+        <v>5</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2631</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>-0.0108</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Caroline Golden Glades</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>36</v>
+      </c>
+      <c r="F35" t="n">
+        <v>33</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1085</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2948</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2789</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2597</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2770</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2515</v>
+      </c>
+      <c r="N35" t="n">
+        <v>19</v>
+      </c>
+      <c r="O35" t="n">
+        <v>15</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2760</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>-0.09030000000000001</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Caroline Golden Glades</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>B2.WFH</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1085</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2893</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2764</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2534</v>
+      </c>
+      <c r="L36" t="n">
+        <v>2660</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2545</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2893</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>-0.0861</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Caroline Golden Glades</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>36</v>
+      </c>
+      <c r="F37" t="n">
+        <v>30</v>
+      </c>
+      <c r="G37" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1221</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3153</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3096</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2816</v>
+      </c>
+      <c r="L37" t="n">
+        <v>3087</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2758</v>
+      </c>
+      <c r="N37" t="n">
+        <v>16</v>
+      </c>
+      <c r="O37" t="n">
+        <v>15</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2984</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>-0.0039</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Caroline Golden Glades</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>B3.WFH</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1221</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2989</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2989</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2529</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2989</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2529</v>
+      </c>
+      <c r="N38" t="n">
+        <v>4</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2989</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.0111</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>10</v>
+      </c>
+      <c r="F39" t="n">
+        <v>10</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>652</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1337</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1367</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1285</v>
+      </c>
+      <c r="N39" t="n">
+        <v>9</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1302</v>
+      </c>
+      <c r="Q39" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>A1A</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>19</v>
+      </c>
+      <c r="F40" t="n">
+        <v>18</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>652</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1340</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1420</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1323</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1378</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1307</v>
+      </c>
+      <c r="N40" t="n">
+        <v>13</v>
+      </c>
+      <c r="O40" t="n">
+        <v>6</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1347</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.0538</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>A1AS</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>19</v>
+      </c>
+      <c r="F41" t="n">
+        <v>17</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" t="n">
+        <v>676</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1388</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1385</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1278</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1419</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1324</v>
+      </c>
+      <c r="N41" t="n">
+        <v>9</v>
+      </c>
+      <c r="O41" t="n">
+        <v>9</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1372</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.0137</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>A1B</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>676</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1384</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1367</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1285</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1384</v>
+      </c>
+      <c r="Q42" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>A1BS</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>676</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1516</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1458</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1516</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1458</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>A1S</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>10</v>
+      </c>
+      <c r="F44" t="n">
+        <v>9</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>676</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1347</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1318</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1248</v>
+      </c>
+      <c r="N44" t="n">
+        <v>3</v>
+      </c>
+      <c r="O44" t="n">
+        <v>7</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1235</v>
+      </c>
+      <c r="Q44" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>19</v>
+      </c>
+      <c r="F45" t="n">
+        <v>18</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>724</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1393</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1470</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1418</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1346</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1290</v>
+      </c>
+      <c r="N45" t="n">
+        <v>10</v>
+      </c>
+      <c r="O45" t="n">
+        <v>9</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1291</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>-0.0134</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>A2A</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>15</v>
+      </c>
+      <c r="F46" t="n">
+        <v>15</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>747</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1429</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1442</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1359</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1296</v>
+      </c>
+      <c r="N46" t="n">
+        <v>5</v>
+      </c>
+      <c r="O46" t="n">
+        <v>10</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1317</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.0578</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>A2AS</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>15</v>
+      </c>
+      <c r="F47" t="n">
+        <v>12</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" t="n">
+        <v>747</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1401</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1542</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1489</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1376</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1299</v>
+      </c>
+      <c r="N47" t="n">
+        <v>9</v>
+      </c>
+      <c r="O47" t="n">
+        <v>6</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1211</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.0167</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>A2B</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>724</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1304</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1470</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1418</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1304</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1221</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1304</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>-0.0134</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>A2BS</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>724</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1415</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1470</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1418</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1427</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1317</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1415</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>-0.0134</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>A2S</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>19</v>
+      </c>
+      <c r="F50" t="n">
+        <v>18</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" t="n">
+        <v>724</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1409</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1466</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1386</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1434</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1357</v>
+      </c>
+      <c r="N50" t="n">
+        <v>5</v>
+      </c>
+      <c r="O50" t="n">
+        <v>13</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1404</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.0195</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>60</v>
+      </c>
+      <c r="F51" t="n">
+        <v>54</v>
+      </c>
+      <c r="G51" t="n">
+        <v>6</v>
+      </c>
+      <c r="H51" t="n">
+        <v>764</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1492</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1535</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1443</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1499</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1411</v>
+      </c>
+      <c r="N51" t="n">
+        <v>33</v>
+      </c>
+      <c r="O51" t="n">
+        <v>23</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1476</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>-0.008</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>A3A</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>10</v>
+      </c>
+      <c r="F52" t="n">
+        <v>7</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" t="n">
+        <v>757</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1370</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1535</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1443</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1499</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1411</v>
+      </c>
+      <c r="N52" t="n">
+        <v>6</v>
+      </c>
+      <c r="O52" t="n">
+        <v>3</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1313</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>-0.008</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>819</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1491</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1454</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1371</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1428</v>
+      </c>
+      <c r="Q53" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>32</v>
+      </c>
+      <c r="F54" t="n">
+        <v>27</v>
+      </c>
+      <c r="G54" t="n">
+        <v>5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>947</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1703</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1893</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1778</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1813</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1737</v>
+      </c>
+      <c r="N54" t="n">
+        <v>13</v>
+      </c>
+      <c r="O54" t="n">
+        <v>15</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1703</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.09470000000000001</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" t="n">
+        <v>20</v>
+      </c>
+      <c r="F55" t="n">
+        <v>18</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2</v>
+      </c>
+      <c r="H55" t="n">
+        <v>956</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1799</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1705</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1610</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1755</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1656</v>
+      </c>
+      <c r="N55" t="n">
+        <v>8</v>
+      </c>
+      <c r="O55" t="n">
+        <v>11</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1730</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>-0.0815</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" t="n">
+        <v>27</v>
+      </c>
+      <c r="F56" t="n">
+        <v>21</v>
+      </c>
+      <c r="G56" t="n">
+        <v>6</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1123</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1888</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1846</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1746</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1875</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1774</v>
+      </c>
+      <c r="N56" t="n">
+        <v>14</v>
+      </c>
+      <c r="O56" t="n">
+        <v>9</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1789</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.0109</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" t="n">
+        <v>9</v>
+      </c>
+      <c r="F57" t="n">
+        <v>6</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1197</v>
+      </c>
+      <c r="I57" t="n">
+        <v>2049</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2150</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2052</v>
+      </c>
+      <c r="L57" t="n">
+        <v>2083</v>
+      </c>
+      <c r="M57" t="n">
+        <v>2004</v>
+      </c>
+      <c r="N57" t="n">
+        <v>6</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1981</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.0149</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>B4A</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1197</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2346</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2150</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2052</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2083</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2004</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0.0149</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F59" t="n">
+        <v>18</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1209</v>
+      </c>
+      <c r="I59" t="n">
+        <v>2027</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1920</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1820</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1965</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1888</v>
+      </c>
+      <c r="N59" t="n">
+        <v>11</v>
+      </c>
+      <c r="O59" t="n">
+        <v>8</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1842</v>
+      </c>
+      <c r="Q59" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" t="n">
+        <v>9</v>
+      </c>
+      <c r="F60" t="n">
+        <v>8</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1444</v>
+      </c>
+      <c r="I60" t="n">
+        <v>2774</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3020</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2913</v>
+      </c>
+      <c r="L60" t="n">
+        <v>2787</v>
+      </c>
+      <c r="M60" t="n">
+        <v>2691</v>
+      </c>
+      <c r="N60" t="n">
+        <v>4</v>
+      </c>
+      <c r="O60" t="n">
+        <v>5</v>
+      </c>
+      <c r="P60" t="n">
+        <v>2785</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.0512</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Pearl Washington</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>C1A</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1444</v>
+      </c>
+      <c r="I61" t="n">
+        <v>2601</v>
+      </c>
+      <c r="J61" t="n">
+        <v>3020</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2913</v>
+      </c>
+      <c r="L61" t="n">
+        <v>2787</v>
+      </c>
+      <c r="M61" t="n">
+        <v>2691</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>2601</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.2878</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>A0</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>8</v>
+      </c>
+      <c r="F62" t="n">
+        <v>7</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="n">
+        <v>624</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1436</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1450</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1392</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3</v>
+      </c>
+      <c r="O62" t="n">
+        <v>4</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1423</v>
+      </c>
+      <c r="Q62" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>7</v>
+      </c>
+      <c r="F63" t="n">
+        <v>7</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>629</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1502</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1528</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1528</v>
+      </c>
+      <c r="N63" t="n">
+        <v>4</v>
+      </c>
+      <c r="O63" t="n">
+        <v>3</v>
+      </c>
+      <c r="P63" t="n">
+        <v>1486</v>
+      </c>
+      <c r="Q63" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>10</v>
+      </c>
+      <c r="F64" t="n">
+        <v>9</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>679</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1541</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1542</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1542</v>
+      </c>
+      <c r="N64" t="n">
+        <v>8</v>
+      </c>
+      <c r="O64" t="n">
+        <v>2</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Q64" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>5</v>
+      </c>
+      <c r="F65" t="n">
+        <v>5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>687</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1503</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1552</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1552</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3</v>
+      </c>
+      <c r="O65" t="n">
+        <v>2</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1455</v>
+      </c>
+      <c r="Q65" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>32</v>
+      </c>
+      <c r="F66" t="n">
+        <v>30</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" t="n">
+        <v>720</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1643</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1775</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1775</v>
+      </c>
+      <c r="L66" t="n">
+        <v>1630</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1630</v>
+      </c>
+      <c r="N66" t="n">
+        <v>9</v>
+      </c>
+      <c r="O66" t="n">
+        <v>21</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1556</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0.0392</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>5</v>
+      </c>
+      <c r="F67" t="n">
+        <v>5</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>759</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1642</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>1687</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1646</v>
+      </c>
+      <c r="N67" t="n">
+        <v>3</v>
+      </c>
+      <c r="O67" t="n">
+        <v>2</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1622</v>
+      </c>
+      <c r="Q67" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>5</v>
+      </c>
+      <c r="F68" t="n">
+        <v>5</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>760</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1607</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>1648</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1648</v>
+      </c>
+      <c r="N68" t="n">
+        <v>2</v>
+      </c>
+      <c r="O68" t="n">
+        <v>3</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1622</v>
+      </c>
+      <c r="Q68" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>762</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1706</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>4</v>
+      </c>
+      <c r="F70" t="n">
+        <v>4</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>769</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1632</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>1656</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1538</v>
+      </c>
+      <c r="N70" t="n">
+        <v>2</v>
+      </c>
+      <c r="O70" t="n">
+        <v>2</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1601</v>
+      </c>
+      <c r="Q70" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>3</v>
+      </c>
+      <c r="F71" t="n">
+        <v>3</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>772</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1667</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1660</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1600</v>
+      </c>
+      <c r="N71" t="n">
+        <v>2</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1654</v>
+      </c>
+      <c r="Q71" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>AA1</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>6</v>
+      </c>
+      <c r="F72" t="n">
+        <v>4</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2</v>
+      </c>
+      <c r="H72" t="n">
+        <v>824</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1604</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1566</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1541</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1602</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1582</v>
+      </c>
+      <c r="N72" t="n">
+        <v>2</v>
+      </c>
+      <c r="O72" t="n">
+        <v>2</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1568</v>
+      </c>
+      <c r="Q72" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>AA2</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>848</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1722</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>1720</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1720</v>
+      </c>
+      <c r="N73" t="n">
+        <v>1</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1680</v>
+      </c>
+      <c r="Q73" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>AA3</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>10</v>
+      </c>
+      <c r="F74" t="n">
+        <v>10</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>872</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1713</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1696</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1565</v>
+      </c>
+      <c r="L74" t="n">
+        <v>1753</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1720</v>
+      </c>
+      <c r="N74" t="n">
+        <v>3</v>
+      </c>
+      <c r="O74" t="n">
+        <v>7</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1685</v>
+      </c>
+      <c r="Q74" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>AA4</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="n">
+        <v>985</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1774</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1734</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1734</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1766</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1766</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1769</v>
+      </c>
+      <c r="Q75" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>AA5</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>3</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1988</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>2125</v>
+      </c>
+      <c r="M76" t="n">
+        <v>2125</v>
+      </c>
+      <c r="N76" t="n">
+        <v>2</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1988</v>
+      </c>
+      <c r="Q76" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>AD1</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>4</v>
+      </c>
+      <c r="F77" t="n">
+        <v>3</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="n">
+        <v>779</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1769</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>1820</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N77" t="n">
+        <v>2</v>
+      </c>
+      <c r="O77" t="n">
+        <v>2</v>
+      </c>
+      <c r="P77" t="n">
+        <v>1806</v>
+      </c>
+      <c r="Q77" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>AD2</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>10</v>
+      </c>
+      <c r="F78" t="n">
+        <v>6</v>
+      </c>
+      <c r="G78" t="n">
+        <v>4</v>
+      </c>
+      <c r="H78" t="n">
+        <v>931</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1912</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1855</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1855</v>
+      </c>
+      <c r="L78" t="n">
+        <v>1860</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1860</v>
+      </c>
+      <c r="N78" t="n">
+        <v>4</v>
+      </c>
+      <c r="O78" t="n">
+        <v>4</v>
+      </c>
+      <c r="P78" t="n">
+        <v>1915</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0.0183</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>AD3</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>20</v>
+      </c>
+      <c r="F79" t="n">
+        <v>20</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>969</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1734</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1714</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1714</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1776</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1776</v>
+      </c>
+      <c r="N79" t="n">
+        <v>9</v>
+      </c>
+      <c r="O79" t="n">
+        <v>11</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1734</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>-0.0061</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>AD4</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>5</v>
+      </c>
+      <c r="F80" t="n">
+        <v>5</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1017</v>
+      </c>
+      <c r="I80" t="n">
+        <v>2003</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>2118</v>
+      </c>
+      <c r="M80" t="n">
+        <v>2118</v>
+      </c>
+      <c r="N80" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" t="n">
+        <v>4</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1943</v>
+      </c>
+      <c r="Q80" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>AD5</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>9</v>
+      </c>
+      <c r="F81" t="n">
+        <v>8</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1076</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2146</v>
+      </c>
+      <c r="J81" t="n">
+        <v>2125</v>
+      </c>
+      <c r="K81" t="n">
+        <v>2125</v>
+      </c>
+      <c r="L81" t="n">
+        <v>2123</v>
+      </c>
+      <c r="M81" t="n">
+        <v>2123</v>
+      </c>
+      <c r="N81" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" t="n">
+        <v>7</v>
+      </c>
+      <c r="P81" t="n">
+        <v>2086</v>
+      </c>
+      <c r="Q81" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" t="n">
+        <v>2</v>
+      </c>
+      <c r="E82" t="n">
+        <v>3</v>
+      </c>
+      <c r="F82" t="n">
+        <v>3</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1093</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1955</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1900</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1783</v>
+      </c>
+      <c r="L82" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1783</v>
+      </c>
+      <c r="N82" t="n">
+        <v>3</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>1955</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>-0.101</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" t="n">
+        <v>2</v>
+      </c>
+      <c r="E83" t="n">
+        <v>20</v>
+      </c>
+      <c r="F83" t="n">
+        <v>20</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1171</v>
+      </c>
+      <c r="I83" t="n">
+        <v>2059</v>
+      </c>
+      <c r="J83" t="n">
+        <v>2064</v>
+      </c>
+      <c r="K83" t="n">
+        <v>2064</v>
+      </c>
+      <c r="L83" t="n">
+        <v>2057</v>
+      </c>
+      <c r="M83" t="n">
+        <v>2045</v>
+      </c>
+      <c r="N83" t="n">
+        <v>7</v>
+      </c>
+      <c r="O83" t="n">
+        <v>13</v>
+      </c>
+      <c r="P83" t="n">
+        <v>2005</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>-0.0183</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" t="n">
+        <v>2</v>
+      </c>
+      <c r="E84" t="n">
+        <v>10</v>
+      </c>
+      <c r="F84" t="n">
+        <v>8</v>
+      </c>
+      <c r="G84" t="n">
+        <v>2</v>
+      </c>
+      <c r="H84" t="n">
+        <v>1198</v>
+      </c>
+      <c r="I84" t="n">
+        <v>2441</v>
+      </c>
+      <c r="J84" t="n">
+        <v>2282</v>
+      </c>
+      <c r="K84" t="n">
+        <v>2282</v>
+      </c>
+      <c r="L84" t="n">
+        <v>2404</v>
+      </c>
+      <c r="M84" t="n">
+        <v>2404</v>
+      </c>
+      <c r="N84" t="n">
+        <v>6</v>
+      </c>
+      <c r="O84" t="n">
+        <v>3</v>
+      </c>
+      <c r="P84" t="n">
+        <v>2356</v>
+      </c>
+      <c r="Q84" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2</v>
+      </c>
+      <c r="D85" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" t="n">
+        <v>10</v>
+      </c>
+      <c r="F85" t="n">
+        <v>9</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1210</v>
+      </c>
+      <c r="I85" t="n">
+        <v>2264</v>
+      </c>
+      <c r="J85" t="n">
+        <v>2193</v>
+      </c>
+      <c r="K85" t="n">
+        <v>2141</v>
+      </c>
+      <c r="L85" t="n">
+        <v>2193</v>
+      </c>
+      <c r="M85" t="n">
+        <v>2141</v>
+      </c>
+      <c r="N85" t="n">
+        <v>3</v>
+      </c>
+      <c r="O85" t="n">
+        <v>7</v>
+      </c>
+      <c r="P85" t="n">
+        <v>2280</v>
+      </c>
+      <c r="Q85" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" t="n">
+        <v>10</v>
+      </c>
+      <c r="F86" t="n">
+        <v>8</v>
+      </c>
+      <c r="G86" t="n">
+        <v>2</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1253</v>
+      </c>
+      <c r="I86" t="n">
+        <v>2396</v>
+      </c>
+      <c r="J86" t="n">
+        <v>2237</v>
+      </c>
+      <c r="K86" t="n">
+        <v>2078</v>
+      </c>
+      <c r="L86" t="n">
+        <v>2307</v>
+      </c>
+      <c r="M86" t="n">
+        <v>2211</v>
+      </c>
+      <c r="N86" t="n">
+        <v>4</v>
+      </c>
+      <c r="O86" t="n">
+        <v>5</v>
+      </c>
+      <c r="P86" t="n">
+        <v>2285</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>-0.076</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" t="n">
+        <v>2</v>
+      </c>
+      <c r="E87" t="n">
+        <v>3</v>
+      </c>
+      <c r="F87" t="n">
+        <v>3</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1253</v>
+      </c>
+      <c r="I87" t="n">
+        <v>2307</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>3</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BD1</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>2</v>
+      </c>
+      <c r="D88" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" t="n">
+        <v>5</v>
+      </c>
+      <c r="F88" t="n">
+        <v>5</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1489</v>
+      </c>
+      <c r="I88" t="n">
+        <v>2873</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>2881</v>
+      </c>
+      <c r="M88" t="n">
+        <v>2830</v>
+      </c>
+      <c r="N88" t="n">
+        <v>2</v>
+      </c>
+      <c r="O88" t="n">
+        <v>3</v>
+      </c>
+      <c r="P88" t="n">
+        <v>2842</v>
+      </c>
+      <c r="Q88" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Pearl 21 Eleven</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>3</v>
+      </c>
+      <c r="D89" t="n">
+        <v>3</v>
+      </c>
+      <c r="E89" t="n">
+        <v>3</v>
+      </c>
+      <c r="F89" t="n">
+        <v>3</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1709</v>
+      </c>
+      <c r="I89" t="n">
+        <v>3338</v>
+      </c>
+      <c r="J89" t="n">
+        <v>3349</v>
+      </c>
+      <c r="K89" t="n">
+        <v>3349</v>
+      </c>
+      <c r="L89" t="n">
+        <v>3432</v>
+      </c>
+      <c r="M89" t="n">
+        <v>3286</v>
+      </c>
+      <c r="N89" t="n">
+        <v>2</v>
+      </c>
+      <c r="O89" t="n">
+        <v>1</v>
+      </c>
+      <c r="P89" t="n">
+        <v>3370</v>
+      </c>
+      <c r="Q89" t="n">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3961,22 +9457,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3997,22 +9500,57 @@
       </c>
       <c r="D1" s="17" t="inlineStr">
         <is>
+          <t>% Earning $100K+</t>
+        </is>
+      </c>
+      <c r="E1" s="17" t="inlineStr">
+        <is>
           <t>Median Personal Income</t>
         </is>
       </c>
-      <c r="E1" s="17" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>Median HH Size</t>
         </is>
       </c>
-      <c r="F1" s="17" t="inlineStr">
+      <c r="G1" s="17" t="inlineStr">
         <is>
           <t>Median Age</t>
         </is>
       </c>
-      <c r="G1" s="17" t="inlineStr">
+      <c r="H1" s="17" t="inlineStr">
         <is>
           <t>Rent-to-Income</t>
+        </is>
+      </c>
+      <c r="I1" s="17" t="inlineStr">
+        <is>
+          <t>Inc &lt;$50K</t>
+        </is>
+      </c>
+      <c r="J1" s="17" t="inlineStr">
+        <is>
+          <t>Inc $50-75K</t>
+        </is>
+      </c>
+      <c r="K1" s="17" t="inlineStr">
+        <is>
+          <t>Inc $75-100K</t>
+        </is>
+      </c>
+      <c r="L1" s="17" t="inlineStr">
+        <is>
+          <t>Inc $100K+</t>
+        </is>
+      </c>
+      <c r="M1" s="17" t="inlineStr">
+        <is>
+          <t>Resident Records</t>
+        </is>
+      </c>
+      <c r="N1" s="17" t="inlineStr">
+        <is>
+          <t>Prospect Leads</t>
         </is>
       </c>
     </row>
@@ -4029,16 +9567,37 @@
         <v>287107</v>
       </c>
       <c r="D2" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="E2" t="n">
         <v>108715</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>1.3</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>41</v>
       </c>
-      <c r="G2" t="n">
-        <v>0.185</v>
+      <c r="H2" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="M2" t="n">
+        <v>456</v>
+      </c>
+      <c r="N2" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -4054,16 +9613,37 @@
         <v>171459</v>
       </c>
       <c r="D3" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="E3" t="n">
         <v>79225</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>33</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>0.236</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="M3" t="n">
+        <v>226</v>
+      </c>
+      <c r="N3" t="n">
+        <v>256</v>
       </c>
     </row>
     <row r="4">
@@ -4079,16 +9659,37 @@
         <v>177989</v>
       </c>
       <c r="D4" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="E4" t="n">
         <v>75000</v>
       </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
       <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
         <v>30</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.205</v>
+      <c r="H4" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="M4" t="n">
+        <v>305</v>
+      </c>
+      <c r="N4" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -4104,16 +9705,37 @@
         <v>264948</v>
       </c>
       <c r="D5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E5" t="n">
         <v>78624</v>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
       <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
         <v>32</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.233</v>
+      <c r="H5" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M5" t="n">
+        <v>206</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/Morgan_Recap_Data_Tape.xlsx
+++ b/output/Morgan_Recap_Data_Tape.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="M16" s="18" t="inlineStr">
         <is>
-          <t>In-Place Cap</t>
+          <t>JLL UW Cap</t>
         </is>
       </c>
       <c r="N16" s="18" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="E26" s="18" t="inlineStr">
         <is>
-          <t>JLL In-Place Cap</t>
+          <t>JLL UW Cap</t>
         </is>
       </c>
       <c r="F26" s="18" t="inlineStr">
@@ -3876,18 +3876,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3903,35 +3909,65 @@
       </c>
       <c r="C1" s="17" t="inlineStr">
         <is>
-          <t>HD Market T90</t>
+          <t>Mkt T12 (HD365 eff)</t>
         </is>
       </c>
       <c r="D1" s="17" t="inlineStr">
         <is>
-          <t>HD Market T365</t>
+          <t>Mkt T3 (HD90 eff)</t>
         </is>
       </c>
       <c r="E1" s="17" t="inlineStr">
         <is>
-          <t>HD Effective T90</t>
+          <t>Mkt T12 (HD365 ask)</t>
         </is>
       </c>
       <c r="F1" s="17" t="inlineStr">
         <is>
-          <t>Loss-to-Lease %</t>
+          <t>Mkt T3 (HD90 ask)</t>
         </is>
       </c>
       <c r="G1" s="17" t="inlineStr">
         <is>
-          <t>HD Concession %</t>
+          <t>Loss-to-Lease T12</t>
         </is>
       </c>
       <c r="H1" s="17" t="inlineStr">
         <is>
-          <t>New-Lease Trade-Out</t>
+          <t>Loss-to-Lease T3</t>
         </is>
       </c>
       <c r="I1" s="17" t="inlineStr">
+        <is>
+          <t>Market Direction (T3 vs T12)</t>
+        </is>
+      </c>
+      <c r="J1" s="17" t="inlineStr">
+        <is>
+          <t>HD Concession T12</t>
+        </is>
+      </c>
+      <c r="K1" s="17" t="inlineStr">
+        <is>
+          <t>HD Concession T3</t>
+        </is>
+      </c>
+      <c r="L1" s="17" t="inlineStr">
+        <is>
+          <t>New-Lease T/O (gross)</t>
+        </is>
+      </c>
+      <c r="M1" s="17" t="inlineStr">
+        <is>
+          <t>New-Lease T/O (eff)</t>
+        </is>
+      </c>
+      <c r="N1" s="17" t="inlineStr">
+        <is>
+          <t>Renewal T/O (gross)</t>
+        </is>
+      </c>
+      <c r="O1" s="17" t="inlineStr">
         <is>
           <t>HD Asking YoY</t>
         </is>
@@ -3947,24 +3983,42 @@
         <v>2296</v>
       </c>
       <c r="C2" t="n">
+        <v>2354</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2442</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2365</v>
+      </c>
+      <c r="F2" t="n">
         <v>2443</v>
       </c>
-      <c r="D2" t="n">
-        <v>2365</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2442</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.064</v>
-      </c>
       <c r="G2" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0374</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="K2" t="n">
         <v>0.0002</v>
       </c>
-      <c r="H2" t="n">
+      <c r="L2" t="n">
         <v>0.0346</v>
       </c>
-      <c r="I2" t="n">
+      <c r="M2" t="n">
+        <v>0.0344</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0309</v>
+      </c>
+      <c r="O2" t="n">
         <v>0.0755</v>
       </c>
     </row>
@@ -3978,24 +4032,42 @@
         <v>2500</v>
       </c>
       <c r="C3" t="n">
+        <v>2246</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2275</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2450</v>
+      </c>
+      <c r="F3" t="n">
         <v>2445</v>
       </c>
-      <c r="D3" t="n">
-        <v>2450</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2275</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-0.0218</v>
-      </c>
       <c r="G3" t="n">
+        <v>-0.1016</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.0901</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0833</v>
+      </c>
+      <c r="K3" t="n">
         <v>0.0699</v>
       </c>
-      <c r="H3" t="n">
+      <c r="L3" t="n">
         <v>-0.1155</v>
       </c>
-      <c r="I3" t="n">
+      <c r="M3" t="n">
+        <v>-0.0941</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="O3" t="n">
         <v>-0.0738</v>
       </c>
     </row>
@@ -4009,24 +4081,42 @@
         <v>1603</v>
       </c>
       <c r="C4" t="n">
+        <v>1534</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1591</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1616</v>
+      </c>
+      <c r="F4" t="n">
         <v>1682</v>
       </c>
-      <c r="D4" t="n">
-        <v>1616</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1591</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.0493</v>
-      </c>
       <c r="G4" t="n">
+        <v>-0.0429</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0373</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0508</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.0538</v>
       </c>
-      <c r="H4" t="n">
+      <c r="L4" t="n">
         <v>-0.1522</v>
       </c>
-      <c r="I4" t="n">
+      <c r="M4" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="O4" t="n">
         <v>0.0163</v>
       </c>
     </row>
@@ -4040,24 +4130,42 @@
         <v>1890</v>
       </c>
       <c r="C5" t="n">
+        <v>1865</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1923</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1887</v>
+      </c>
+      <c r="F5" t="n">
         <v>1950</v>
       </c>
-      <c r="D5" t="n">
-        <v>1887</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1923</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.0318</v>
-      </c>
       <c r="G5" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0309</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="K5" t="n">
         <v>0.0139</v>
       </c>
-      <c r="H5" t="n">
+      <c r="L5" t="n">
         <v>-0.0701</v>
       </c>
-      <c r="I5" t="n">
+      <c r="M5" t="n">
+        <v>-0.0955</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="O5" t="n">
         <v>-0.0012</v>
       </c>
     </row>

--- a/output/Morgan_Recap_Data_Tape.xlsx
+++ b/output/Morgan_Recap_Data_Tape.xlsx
@@ -806,7 +806,7 @@
       <c r="G7" s="7" t="n"/>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BLENDED GOING-IN CAP</t>
+          <t xml:space="preserve"> BLENDED JLL UW CAP</t>
         </is>
       </c>
       <c r="J7" s="6" t="n"/>
@@ -910,7 +910,7 @@
       <c r="G10" s="7" t="n"/>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JLL Yr-0 NOI ÷ price</t>
+          <t xml:space="preserve"> JLL UW Yr-0 NOI ÷ price</t>
         </is>
       </c>
       <c r="J10" s="6" t="n"/>
@@ -947,7 +947,7 @@
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Act Cap = trailing-12 NOI ÷ ask · JLL Cap = underwritten Year-0 (in-place) NOI ÷ price · New T/O = rent-weighted new-lease trade-out vs prior lease (Yardi LTO, T90)</t>
+          <t>Act Cap = trailing-12 NOI ÷ ask · JLL UW Cap = JLL underwritten Year-0 (in-place) NOI ÷ price · Contract /mo = T1 AGPR ÷ units · New T/O = rent-weighted new-lease trade-out vs prior lease (Yardi LTO, T90)</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="I16" s="18" t="inlineStr">
         <is>
-          <t>In-Place /mo</t>
+          <t>Contract /mo</t>
         </is>
       </c>
       <c r="J16" s="18" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="P16" s="18" t="inlineStr">
         <is>
-          <t>Lev IRR</t>
+          <t>JLL UW LIRR</t>
         </is>
       </c>
       <c r="Q16" s="18" t="inlineStr">
@@ -1057,7 +1057,7 @@
         <v>0.9694989106753813</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>2295.846846846847</v>
+        <v>2330.481481481481</v>
       </c>
       <c r="J17" s="25" t="n">
         <v>0.03463420147578833</v>
@@ -1108,7 +1108,7 @@
         <v>0.923728813559322</v>
       </c>
       <c r="I18" s="33" t="n">
-        <v>2499.940366972477</v>
+        <v>2528.881355932203</v>
       </c>
       <c r="J18" s="34" t="n">
         <v>-0.115485050906139</v>
@@ -1159,7 +1159,7 @@
         <v>0.937888198757764</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>1603</v>
+        <v>1687.074534161491</v>
       </c>
       <c r="J19" s="25" t="n">
         <v>-0.1521936575618804</v>
@@ -1210,7 +1210,7 @@
         <v>0.9488372093023256</v>
       </c>
       <c r="I20" s="33" t="n">
-        <v>1889.813725490196</v>
+        <v>1940.772093023256</v>
       </c>
       <c r="J20" s="34" t="n">
         <v>-0.07013679161485165</v>
@@ -2569,7 +2569,7 @@
         <v>41</v>
       </c>
       <c r="H2" t="n">
-        <v>0.184</v>
+        <v>0.188</v>
       </c>
       <c r="I2" t="n">
         <v>0.02</v>
@@ -2615,7 +2615,7 @@
         <v>33</v>
       </c>
       <c r="H3" t="n">
-        <v>0.236</v>
+        <v>0.24</v>
       </c>
       <c r="I3" t="n">
         <v>0.013</v>
@@ -2661,7 +2661,7 @@
         <v>30</v>
       </c>
       <c r="H4" t="n">
-        <v>0.207</v>
+        <v>0.214</v>
       </c>
       <c r="I4" t="n">
         <v>0.034</v>
@@ -2707,7 +2707,7 @@
         <v>32</v>
       </c>
       <c r="H5" t="n">
-        <v>0.234</v>
+        <v>0.24</v>
       </c>
       <c r="I5" t="n">
         <v>0.031</v>
@@ -3876,24 +3876,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3904,70 +3907,85 @@
       </c>
       <c r="B1" s="17" t="inlineStr">
         <is>
-          <t>In-Place Rent</t>
+          <t>Contract Rent (T1 AGPR/unit)</t>
         </is>
       </c>
       <c r="C1" s="17" t="inlineStr">
         <is>
+          <t>Avg In-Place (occupied)</t>
+        </is>
+      </c>
+      <c r="D1" s="17" t="inlineStr">
+        <is>
           <t>Mkt T12 (HD365 eff)</t>
         </is>
       </c>
-      <c r="D1" s="17" t="inlineStr">
+      <c r="E1" s="17" t="inlineStr">
         <is>
           <t>Mkt T3 (HD90 eff)</t>
         </is>
       </c>
-      <c r="E1" s="17" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>Mkt T12 (HD365 ask)</t>
         </is>
       </c>
-      <c r="F1" s="17" t="inlineStr">
+      <c r="G1" s="17" t="inlineStr">
         <is>
           <t>Mkt T3 (HD90 ask)</t>
         </is>
       </c>
-      <c r="G1" s="17" t="inlineStr">
-        <is>
-          <t>Loss-to-Lease T12</t>
-        </is>
-      </c>
       <c r="H1" s="17" t="inlineStr">
         <is>
-          <t>Loss-to-Lease T3</t>
+          <t>HD365 leases (n)</t>
         </is>
       </c>
       <c r="I1" s="17" t="inlineStr">
         <is>
+          <t>HD90 leases (n)</t>
+        </is>
+      </c>
+      <c r="J1" s="17" t="inlineStr">
+        <is>
+          <t>Contract vs Mkt T12</t>
+        </is>
+      </c>
+      <c r="K1" s="17" t="inlineStr">
+        <is>
+          <t>Contract vs Mkt T3</t>
+        </is>
+      </c>
+      <c r="L1" s="17" t="inlineStr">
+        <is>
           <t>Market Direction (T3 vs T12)</t>
         </is>
       </c>
-      <c r="J1" s="17" t="inlineStr">
+      <c r="M1" s="17" t="inlineStr">
         <is>
           <t>HD Concession T12</t>
         </is>
       </c>
-      <c r="K1" s="17" t="inlineStr">
+      <c r="N1" s="17" t="inlineStr">
         <is>
           <t>HD Concession T3</t>
         </is>
       </c>
-      <c r="L1" s="17" t="inlineStr">
+      <c r="O1" s="17" t="inlineStr">
         <is>
           <t>New-Lease T/O (gross)</t>
         </is>
       </c>
-      <c r="M1" s="17" t="inlineStr">
+      <c r="P1" s="17" t="inlineStr">
         <is>
           <t>New-Lease T/O (eff)</t>
         </is>
       </c>
-      <c r="N1" s="17" t="inlineStr">
+      <c r="Q1" s="17" t="inlineStr">
         <is>
           <t>Renewal T/O (gross)</t>
         </is>
       </c>
-      <c r="O1" s="17" t="inlineStr">
+      <c r="R1" s="17" t="inlineStr">
         <is>
           <t>HD Asking YoY</t>
         </is>
@@ -3980,45 +3998,54 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2296</v>
+        <v>2330</v>
       </c>
       <c r="C2" t="n">
+        <v>2343</v>
+      </c>
+      <c r="D2" t="n">
         <v>2354</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>2442</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>2365</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>2443</v>
       </c>
-      <c r="G2" t="n">
-        <v>0.0254</v>
-      </c>
       <c r="H2" t="n">
-        <v>0.0638</v>
+        <v>207</v>
       </c>
       <c r="I2" t="n">
+        <v>62</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="L2" t="n">
         <v>0.0374</v>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
         <v>0.0045</v>
       </c>
-      <c r="K2" t="n">
+      <c r="N2" t="n">
         <v>0.0002</v>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>0.0346</v>
       </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
         <v>0.0344</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>0.0309</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>0.0755</v>
       </c>
     </row>
@@ -4029,45 +4056,54 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2500</v>
+        <v>2529</v>
       </c>
       <c r="C3" t="n">
+        <v>2534</v>
+      </c>
+      <c r="D3" t="n">
         <v>2246</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>2275</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>2450</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>2445</v>
       </c>
-      <c r="G3" t="n">
-        <v>-0.1016</v>
-      </c>
       <c r="H3" t="n">
-        <v>-0.0901</v>
+        <v>104</v>
       </c>
       <c r="I3" t="n">
+        <v>53</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.1119</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-0.1005</v>
+      </c>
+      <c r="L3" t="n">
         <v>0.0128</v>
       </c>
-      <c r="J3" t="n">
+      <c r="M3" t="n">
         <v>0.0833</v>
       </c>
-      <c r="K3" t="n">
+      <c r="N3" t="n">
         <v>0.0699</v>
       </c>
-      <c r="L3" t="n">
+      <c r="O3" t="n">
         <v>-0.1155</v>
       </c>
-      <c r="M3" t="n">
+      <c r="P3" t="n">
         <v>-0.0941</v>
       </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
         <v>0.0274</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
         <v>-0.0738</v>
       </c>
     </row>
@@ -4078,45 +4114,54 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1603</v>
+        <v>1687</v>
       </c>
       <c r="C4" t="n">
+        <v>1658</v>
+      </c>
+      <c r="D4" t="n">
         <v>1534</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>1591</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>1616</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>1682</v>
       </c>
-      <c r="G4" t="n">
-        <v>-0.0429</v>
-      </c>
       <c r="H4" t="n">
-        <v>-0.0072</v>
+        <v>232</v>
       </c>
       <c r="I4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.0906</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.0567</v>
+      </c>
+      <c r="L4" t="n">
         <v>0.0373</v>
       </c>
-      <c r="J4" t="n">
+      <c r="M4" t="n">
         <v>0.0508</v>
       </c>
-      <c r="K4" t="n">
+      <c r="N4" t="n">
         <v>0.0538</v>
       </c>
-      <c r="L4" t="n">
+      <c r="O4" t="n">
         <v>-0.1522</v>
       </c>
-      <c r="M4" t="n">
+      <c r="P4" t="n">
         <v>-0.19</v>
       </c>
-      <c r="N4" t="n">
+      <c r="Q4" t="n">
         <v>0.0321</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>0.0163</v>
       </c>
     </row>
@@ -4127,45 +4172,54 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1890</v>
+        <v>1941</v>
       </c>
       <c r="C5" t="n">
+        <v>1942</v>
+      </c>
+      <c r="D5" t="n">
         <v>1865</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>1923</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1887</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>1950</v>
       </c>
-      <c r="G5" t="n">
-        <v>-0.013</v>
-      </c>
       <c r="H5" t="n">
-        <v>0.0175</v>
+        <v>80</v>
       </c>
       <c r="I5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.0389</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.0092</v>
+      </c>
+      <c r="L5" t="n">
         <v>0.0309</v>
       </c>
-      <c r="J5" t="n">
+      <c r="M5" t="n">
         <v>0.0114</v>
       </c>
-      <c r="K5" t="n">
+      <c r="N5" t="n">
         <v>0.0139</v>
       </c>
-      <c r="L5" t="n">
+      <c r="O5" t="n">
         <v>-0.0701</v>
       </c>
-      <c r="M5" t="n">
+      <c r="P5" t="n">
         <v>-0.0955</v>
       </c>
-      <c r="N5" t="n">
+      <c r="Q5" t="n">
         <v>0.016</v>
       </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
         <v>-0.0012</v>
       </c>
     </row>
@@ -5386,7 +5440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5400,9 +5454,11 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5463,15 +5519,25 @@
       </c>
       <c r="L1" s="17" t="inlineStr">
         <is>
+          <t>HD365 leases (n)</t>
+        </is>
+      </c>
+      <c r="M1" s="17" t="inlineStr">
+        <is>
+          <t>HD90 leases (n)</t>
+        </is>
+      </c>
+      <c r="N1" s="17" t="inlineStr">
+        <is>
           <t>HD Ask YoY</t>
         </is>
       </c>
-      <c r="M1" s="17" t="inlineStr">
+      <c r="O1" s="17" t="inlineStr">
         <is>
           <t>T12 Conc % EGR</t>
         </is>
       </c>
-      <c r="N1" s="17" t="inlineStr">
+      <c r="P1" s="17" t="inlineStr">
         <is>
           <t>30+ Delinq % GPR</t>
         </is>
@@ -5493,10 +5559,10 @@
         <v>0.9913</v>
       </c>
       <c r="E2" t="n">
-        <v>2296</v>
+        <v>2343</v>
       </c>
       <c r="F2" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G2" t="n">
         <v>0.0585</v>
@@ -5514,12 +5580,18 @@
         <v>2442</v>
       </c>
       <c r="L2" t="n">
+        <v>207</v>
+      </c>
+      <c r="M2" t="n">
+        <v>62</v>
+      </c>
+      <c r="N2" t="n">
         <v>0.0755</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>0.0015</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0.0007</v>
       </c>
     </row>
@@ -5539,10 +5611,10 @@
         <v>0.9915</v>
       </c>
       <c r="E3" t="n">
-        <v>2500</v>
+        <v>2534</v>
       </c>
       <c r="F3" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0021</v>
@@ -5560,12 +5632,18 @@
         <v>2275</v>
       </c>
       <c r="L3" t="n">
+        <v>104</v>
+      </c>
+      <c r="M3" t="n">
+        <v>53</v>
+      </c>
+      <c r="N3" t="n">
         <v>-0.0738</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>0.06569999999999999</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>-0.0015</v>
       </c>
     </row>
@@ -5585,10 +5663,10 @@
         <v>0.9969</v>
       </c>
       <c r="E4" t="n">
-        <v>1603</v>
+        <v>1658</v>
       </c>
       <c r="F4" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0266</v>
@@ -5606,12 +5684,18 @@
         <v>1591</v>
       </c>
       <c r="L4" t="n">
+        <v>232</v>
+      </c>
+      <c r="M4" t="n">
+        <v>80</v>
+      </c>
+      <c r="N4" t="n">
         <v>0.0163</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>0.0125</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.0038</v>
       </c>
     </row>
@@ -5631,10 +5715,10 @@
         <v>0.9953</v>
       </c>
       <c r="E5" t="n">
-        <v>1890</v>
+        <v>1942</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0097</v>
@@ -5652,12 +5736,18 @@
         <v>1923</v>
       </c>
       <c r="L5" t="n">
+        <v>80</v>
+      </c>
+      <c r="M5" t="n">
+        <v>26</v>
+      </c>
+      <c r="N5" t="n">
         <v>-0.0012</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>0.0022</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -5811,7 +5901,7 @@
         <v>657</v>
       </c>
       <c r="I2" t="n">
-        <v>1478</v>
+        <v>1510</v>
       </c>
       <c r="J2" t="n">
         <v>1535</v>
@@ -5832,7 +5922,7 @@
         <v>14</v>
       </c>
       <c r="P2" t="n">
-        <v>1427</v>
+        <v>1454</v>
       </c>
       <c r="Q2" t="n">
         <v/>
@@ -5868,7 +5958,7 @@
         <v>695</v>
       </c>
       <c r="I3" t="n">
-        <v>1557</v>
+        <v>1608</v>
       </c>
       <c r="J3" t="n">
         <v>1689</v>
@@ -5889,7 +5979,7 @@
         <v>36</v>
       </c>
       <c r="P3" t="n">
-        <v>1588</v>
+        <v>1615</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.005</v>
@@ -5925,7 +6015,7 @@
         <v>754</v>
       </c>
       <c r="I4" t="n">
-        <v>1638</v>
+        <v>1635</v>
       </c>
       <c r="J4" t="n">
         <v>1740</v>
@@ -5946,7 +6036,7 @@
         <v>10</v>
       </c>
       <c r="P4" t="n">
-        <v>1652</v>
+        <v>1668</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0968</v>
@@ -5982,7 +6072,7 @@
         <v>776</v>
       </c>
       <c r="I5" t="n">
-        <v>1709</v>
+        <v>1736</v>
       </c>
       <c r="J5" t="n">
         <v>1784</v>
@@ -6003,7 +6093,7 @@
         <v>10</v>
       </c>
       <c r="P5" t="n">
-        <v>1626</v>
+        <v>1658</v>
       </c>
       <c r="Q5" t="n">
         <v>0.0513</v>
@@ -6039,7 +6129,7 @@
         <v>739</v>
       </c>
       <c r="I6" t="n">
-        <v>1646</v>
+        <v>1702</v>
       </c>
       <c r="J6" t="n">
         <v>1781</v>
@@ -6060,7 +6150,7 @@
         <v>10</v>
       </c>
       <c r="P6" t="n">
-        <v>1606</v>
+        <v>1674</v>
       </c>
       <c r="Q6" t="n">
         <v>0.0495</v>
@@ -6096,7 +6186,7 @@
         <v>887</v>
       </c>
       <c r="I7" t="n">
-        <v>1736</v>
+        <v>1769</v>
       </c>
       <c r="J7" t="n">
         <v>1840</v>
@@ -6117,7 +6207,7 @@
         <v>10</v>
       </c>
       <c r="P7" t="n">
-        <v>1695</v>
+        <v>1745</v>
       </c>
       <c r="Q7" t="n">
         <v>0.0297</v>
@@ -6153,7 +6243,7 @@
         <v>834</v>
       </c>
       <c r="I8" t="n">
-        <v>1649</v>
+        <v>1698</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -6174,7 +6264,7 @@
         <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>1671</v>
+        <v>1706</v>
       </c>
       <c r="Q8" t="n">
         <v/>
@@ -6210,7 +6300,7 @@
         <v>822</v>
       </c>
       <c r="I9" t="n">
-        <v>1827</v>
+        <v>1899</v>
       </c>
       <c r="J9" t="n">
         <v>1812</v>
@@ -6231,7 +6321,7 @@
         <v>7</v>
       </c>
       <c r="P9" t="n">
-        <v>1625</v>
+        <v>1685</v>
       </c>
       <c r="Q9" t="n">
         <v>0.063</v>
@@ -6267,7 +6357,7 @@
         <v>896</v>
       </c>
       <c r="I10" t="n">
-        <v>1706</v>
+        <v>1776</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -6288,7 +6378,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1706</v>
+        <v>1776</v>
       </c>
       <c r="Q10" t="n">
         <v/>
@@ -6324,7 +6414,7 @@
         <v>904</v>
       </c>
       <c r="I11" t="n">
-        <v>1761</v>
+        <v>1834</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -6345,7 +6435,7 @@
         <v>7</v>
       </c>
       <c r="P11" t="n">
-        <v>1779</v>
+        <v>1841</v>
       </c>
       <c r="Q11" t="n">
         <v/>
@@ -6381,7 +6471,7 @@
         <v>866</v>
       </c>
       <c r="I12" t="n">
-        <v>1673</v>
+        <v>1723</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -6438,7 +6528,7 @@
         <v>948</v>
       </c>
       <c r="I13" t="n">
-        <v>2001</v>
+        <v>2048</v>
       </c>
       <c r="J13" t="n">
         <v>1988</v>
@@ -6459,7 +6549,7 @@
         <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>1970</v>
+        <v>2009</v>
       </c>
       <c r="Q13" t="n">
         <v>0.0277</v>
@@ -6552,7 +6642,7 @@
         <v>1082</v>
       </c>
       <c r="I15" t="n">
-        <v>1984</v>
+        <v>1987</v>
       </c>
       <c r="J15" t="n">
         <v>2052</v>
@@ -6573,7 +6663,7 @@
         <v>17</v>
       </c>
       <c r="P15" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="Q15" t="n">
         <v>0.048</v>
@@ -6609,7 +6699,7 @@
         <v>1022</v>
       </c>
       <c r="I16" t="n">
-        <v>2084</v>
+        <v>2088</v>
       </c>
       <c r="J16" t="n">
         <v>2052</v>
@@ -6630,7 +6720,7 @@
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>2026</v>
+        <v>2000</v>
       </c>
       <c r="Q16" t="n">
         <v>0.048</v>
@@ -6666,7 +6756,7 @@
         <v>1374</v>
       </c>
       <c r="I17" t="n">
-        <v>2570</v>
+        <v>2621</v>
       </c>
       <c r="J17" t="n">
         <v>2584</v>
@@ -6687,7 +6777,7 @@
         <v>10</v>
       </c>
       <c r="P17" t="n">
-        <v>2601</v>
+        <v>2649</v>
       </c>
       <c r="Q17" t="n">
         <v>0.0287</v>
@@ -6723,7 +6813,7 @@
         <v>1098</v>
       </c>
       <c r="I18" t="n">
-        <v>2381</v>
+        <v>2357</v>
       </c>
       <c r="J18" t="n">
         <v>2557</v>
@@ -6744,7 +6834,7 @@
         <v>13</v>
       </c>
       <c r="P18" t="n">
-        <v>2525</v>
+        <v>2475</v>
       </c>
       <c r="Q18" t="n">
         <v>0.1508</v>
@@ -6780,7 +6870,7 @@
         <v>1278</v>
       </c>
       <c r="I19" t="n">
-        <v>2350</v>
+        <v>2337</v>
       </c>
       <c r="J19" t="n">
         <v>2627</v>
@@ -6801,7 +6891,7 @@
         <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>2422</v>
+        <v>2436</v>
       </c>
       <c r="Q19" t="n">
         <v>0.1462</v>
@@ -6837,7 +6927,7 @@
         <v>1330</v>
       </c>
       <c r="I20" t="n">
-        <v>2366</v>
+        <v>2346</v>
       </c>
       <c r="J20" t="n">
         <v>2557</v>
@@ -6858,7 +6948,7 @@
         <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>2302</v>
+        <v>2272</v>
       </c>
       <c r="Q20" t="n">
         <v>0.1375</v>
@@ -6894,7 +6984,7 @@
         <v>1486</v>
       </c>
       <c r="I21" t="n">
-        <v>2941</v>
+        <v>3006</v>
       </c>
       <c r="J21" t="n">
         <v>3153</v>
@@ -6915,7 +7005,7 @@
         <v>18</v>
       </c>
       <c r="P21" t="n">
-        <v>2927</v>
+        <v>2980</v>
       </c>
       <c r="Q21" t="n">
         <v>0.0837</v>
@@ -6951,7 +7041,7 @@
         <v>750</v>
       </c>
       <c r="I22" t="n">
-        <v>1571</v>
+        <v>1653</v>
       </c>
       <c r="J22" t="n">
         <v>1651</v>
@@ -6972,7 +7062,7 @@
         <v>6</v>
       </c>
       <c r="P22" t="n">
-        <v>1567</v>
+        <v>1654</v>
       </c>
       <c r="Q22" t="n">
         <v>0.0677</v>
@@ -7008,7 +7098,7 @@
         <v>1144</v>
       </c>
       <c r="I23" t="n">
-        <v>2139</v>
+        <v>2240</v>
       </c>
       <c r="J23" t="n">
         <v>2267</v>
@@ -7029,7 +7119,7 @@
         <v>16</v>
       </c>
       <c r="P23" t="n">
-        <v>2205</v>
+        <v>2290</v>
       </c>
       <c r="Q23" t="n">
         <v>0.0398</v>
@@ -7065,7 +7155,7 @@
         <v>1164</v>
       </c>
       <c r="I24" t="n">
-        <v>2122</v>
+        <v>2239</v>
       </c>
       <c r="J24" t="n">
         <v>2279</v>
@@ -7086,7 +7176,7 @@
         <v>2</v>
       </c>
       <c r="P24" t="n">
-        <v>2165</v>
+        <v>2287</v>
       </c>
       <c r="Q24" t="n">
         <v/>
@@ -7122,7 +7212,7 @@
         <v>1149</v>
       </c>
       <c r="I25" t="n">
-        <v>2415</v>
+        <v>2495</v>
       </c>
       <c r="J25" t="n">
         <v>2290</v>
@@ -7143,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2415</v>
+        <v>2495</v>
       </c>
       <c r="Q25" t="n">
         <v/>
@@ -7179,7 +7269,7 @@
         <v>2220</v>
       </c>
       <c r="I26" t="n">
-        <v>4124</v>
+        <v>4192</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -7200,7 +7290,7 @@
         <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>4083</v>
+        <v>4108</v>
       </c>
       <c r="Q26" t="n">
         <v/>
@@ -7236,7 +7326,7 @@
         <v>1511</v>
       </c>
       <c r="I27" t="n">
-        <v>3151</v>
+        <v>3195</v>
       </c>
       <c r="J27" t="n">
         <v>3506</v>
@@ -7257,7 +7347,7 @@
         <v>14</v>
       </c>
       <c r="P27" t="n">
-        <v>3090</v>
+        <v>3141</v>
       </c>
       <c r="Q27" t="n">
         <v>0.1236</v>
@@ -7293,7 +7383,7 @@
         <v>1659</v>
       </c>
       <c r="I28" t="n">
-        <v>3255</v>
+        <v>3310</v>
       </c>
       <c r="J28" t="n">
         <v>3940</v>
@@ -7314,7 +7404,7 @@
         <v>7</v>
       </c>
       <c r="P28" t="n">
-        <v>3204</v>
+        <v>3253</v>
       </c>
       <c r="Q28" t="n">
         <v>0.2217</v>
@@ -7350,7 +7440,7 @@
         <v>1483</v>
       </c>
       <c r="I29" t="n">
-        <v>2661</v>
+        <v>2744</v>
       </c>
       <c r="J29" t="n">
         <v>3180</v>
@@ -7371,7 +7461,7 @@
         <v>11</v>
       </c>
       <c r="P29" t="n">
-        <v>2751</v>
+        <v>2841</v>
       </c>
       <c r="Q29" t="n">
         <v>0.1587</v>
@@ -7407,7 +7497,7 @@
         <v>1637</v>
       </c>
       <c r="I30" t="n">
-        <v>3549</v>
+        <v>3587</v>
       </c>
       <c r="J30" t="n">
         <v>3829</v>
@@ -7428,7 +7518,7 @@
         <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>3554</v>
+        <v>3589</v>
       </c>
       <c r="Q30" t="n">
         <v>0.1433</v>
@@ -7464,7 +7554,7 @@
         <v>1995</v>
       </c>
       <c r="I31" t="n">
-        <v>4030</v>
+        <v>4112</v>
       </c>
       <c r="J31" t="n">
         <v>5151</v>
@@ -7485,7 +7575,7 @@
         <v>7</v>
       </c>
       <c r="P31" t="n">
-        <v>3960</v>
+        <v>4022</v>
       </c>
       <c r="Q31" t="n">
         <v>0.3243</v>
@@ -7521,7 +7611,7 @@
         <v>2256</v>
       </c>
       <c r="I32" t="n">
-        <v>5036</v>
+        <v>5149</v>
       </c>
       <c r="J32" t="n">
         <v>5053</v>
@@ -7542,7 +7632,7 @@
         <v>8</v>
       </c>
       <c r="P32" t="n">
-        <v>4902</v>
+        <v>4969</v>
       </c>
       <c r="Q32" t="n">
         <v/>
@@ -7578,7 +7668,7 @@
         <v>1866</v>
       </c>
       <c r="I33" t="n">
-        <v>3516</v>
+        <v>3591</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -7599,7 +7689,7 @@
         <v>6</v>
       </c>
       <c r="P33" t="n">
-        <v>3414</v>
+        <v>3497</v>
       </c>
       <c r="Q33" t="n">
         <v/>
@@ -7635,7 +7725,7 @@
         <v>585</v>
       </c>
       <c r="I34" t="n">
-        <v>1862</v>
+        <v>1918</v>
       </c>
       <c r="J34" t="n">
         <v>1826</v>
@@ -7656,7 +7746,7 @@
         <v>18</v>
       </c>
       <c r="P34" t="n">
-        <v>1749</v>
+        <v>1789</v>
       </c>
       <c r="Q34" t="n">
         <v>-0.1104</v>
@@ -7692,7 +7782,7 @@
         <v>585</v>
       </c>
       <c r="I35" t="n">
-        <v>1953</v>
+        <v>1965</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -7749,7 +7839,7 @@
         <v>768</v>
       </c>
       <c r="I36" t="n">
-        <v>2249</v>
+        <v>2274</v>
       </c>
       <c r="J36" t="n">
         <v>2153</v>
@@ -7770,7 +7860,7 @@
         <v>39</v>
       </c>
       <c r="P36" t="n">
-        <v>2132</v>
+        <v>2145</v>
       </c>
       <c r="Q36" t="n">
         <v>-0.0949</v>
@@ -7806,7 +7896,7 @@
         <v>768</v>
       </c>
       <c r="I37" t="n">
-        <v>2245</v>
+        <v>2258</v>
       </c>
       <c r="J37" t="n">
         <v>2153</v>
@@ -7827,7 +7917,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="n">
-        <v>2194</v>
+        <v>2214</v>
       </c>
       <c r="Q37" t="n">
         <v>-0.0917</v>
@@ -7863,7 +7953,7 @@
         <v>790</v>
       </c>
       <c r="I38" t="n">
-        <v>2356</v>
+        <v>2395</v>
       </c>
       <c r="J38" t="n">
         <v>2300</v>
@@ -7884,7 +7974,7 @@
         <v>8</v>
       </c>
       <c r="P38" t="n">
-        <v>2231</v>
+        <v>2275</v>
       </c>
       <c r="Q38" t="n">
         <v>-0.08799999999999999</v>
@@ -7920,7 +8010,7 @@
         <v>790</v>
       </c>
       <c r="I39" t="n">
-        <v>2267</v>
+        <v>2294</v>
       </c>
       <c r="J39" t="n">
         <v>2104</v>
@@ -7977,7 +8067,7 @@
         <v>767</v>
       </c>
       <c r="I40" t="n">
-        <v>2408</v>
+        <v>2440</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -7998,7 +8088,7 @@
         <v>2</v>
       </c>
       <c r="P40" t="n">
-        <v>2411</v>
+        <v>2448</v>
       </c>
       <c r="Q40" t="n">
         <v/>
@@ -8034,7 +8124,7 @@
         <v>1071</v>
       </c>
       <c r="I41" t="n">
-        <v>2805</v>
+        <v>2823</v>
       </c>
       <c r="J41" t="n">
         <v>2928</v>
@@ -8055,7 +8145,7 @@
         <v>5</v>
       </c>
       <c r="P41" t="n">
-        <v>2631</v>
+        <v>2656</v>
       </c>
       <c r="Q41" t="n">
         <v>-0.0108</v>
@@ -8091,7 +8181,7 @@
         <v>1085</v>
       </c>
       <c r="I42" t="n">
-        <v>2948</v>
+        <v>2982</v>
       </c>
       <c r="J42" t="n">
         <v>2789</v>
@@ -8112,7 +8202,7 @@
         <v>15</v>
       </c>
       <c r="P42" t="n">
-        <v>2760</v>
+        <v>2809</v>
       </c>
       <c r="Q42" t="n">
         <v>-0.09030000000000001</v>
@@ -8148,7 +8238,7 @@
         <v>1085</v>
       </c>
       <c r="I43" t="n">
-        <v>2893</v>
+        <v>2903</v>
       </c>
       <c r="J43" t="n">
         <v>2764</v>
@@ -8169,7 +8259,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2893</v>
+        <v>2903</v>
       </c>
       <c r="Q43" t="n">
         <v>-0.0861</v>
@@ -8205,7 +8295,7 @@
         <v>1221</v>
       </c>
       <c r="I44" t="n">
-        <v>3153</v>
+        <v>3207</v>
       </c>
       <c r="J44" t="n">
         <v>3096</v>
@@ -8226,7 +8316,7 @@
         <v>15</v>
       </c>
       <c r="P44" t="n">
-        <v>2984</v>
+        <v>3056</v>
       </c>
       <c r="Q44" t="n">
         <v>-0.0039</v>
@@ -8262,7 +8352,7 @@
         <v>1221</v>
       </c>
       <c r="I45" t="n">
-        <v>2989</v>
+        <v>2965</v>
       </c>
       <c r="J45" t="n">
         <v>2989</v>
@@ -8283,7 +8373,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2989</v>
+        <v>2965</v>
       </c>
       <c r="Q45" t="n">
         <v>0.0111</v>
@@ -8319,7 +8409,7 @@
         <v>652</v>
       </c>
       <c r="I46" t="n">
-        <v>1337</v>
+        <v>1392</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -8340,7 +8430,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="n">
-        <v>1302</v>
+        <v>1342</v>
       </c>
       <c r="Q46" t="n">
         <v/>
@@ -8376,7 +8466,7 @@
         <v>652</v>
       </c>
       <c r="I47" t="n">
-        <v>1340</v>
+        <v>1377</v>
       </c>
       <c r="J47" t="n">
         <v>1420</v>
@@ -8397,7 +8487,7 @@
         <v>6</v>
       </c>
       <c r="P47" t="n">
-        <v>1347</v>
+        <v>1417</v>
       </c>
       <c r="Q47" t="n">
         <v>0.0538</v>
@@ -8433,7 +8523,7 @@
         <v>676</v>
       </c>
       <c r="I48" t="n">
-        <v>1388</v>
+        <v>1438</v>
       </c>
       <c r="J48" t="n">
         <v>1385</v>
@@ -8454,7 +8544,7 @@
         <v>9</v>
       </c>
       <c r="P48" t="n">
-        <v>1372</v>
+        <v>1462</v>
       </c>
       <c r="Q48" t="n">
         <v>0.0137</v>
@@ -8604,7 +8694,7 @@
         <v>676</v>
       </c>
       <c r="I51" t="n">
-        <v>1347</v>
+        <v>1402</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -8625,7 +8715,7 @@
         <v>7</v>
       </c>
       <c r="P51" t="n">
-        <v>1235</v>
+        <v>1298</v>
       </c>
       <c r="Q51" t="n">
         <v/>
@@ -8661,7 +8751,7 @@
         <v>724</v>
       </c>
       <c r="I52" t="n">
-        <v>1393</v>
+        <v>1438</v>
       </c>
       <c r="J52" t="n">
         <v>1470</v>
@@ -8682,7 +8772,7 @@
         <v>9</v>
       </c>
       <c r="P52" t="n">
-        <v>1291</v>
+        <v>1321</v>
       </c>
       <c r="Q52" t="n">
         <v>-0.0134</v>
@@ -8718,7 +8808,7 @@
         <v>747</v>
       </c>
       <c r="I53" t="n">
-        <v>1429</v>
+        <v>1479</v>
       </c>
       <c r="J53" t="n">
         <v>1500</v>
@@ -8739,7 +8829,7 @@
         <v>10</v>
       </c>
       <c r="P53" t="n">
-        <v>1317</v>
+        <v>1357</v>
       </c>
       <c r="Q53" t="n">
         <v>0.0578</v>
@@ -8775,7 +8865,7 @@
         <v>747</v>
       </c>
       <c r="I54" t="n">
-        <v>1401</v>
+        <v>1451</v>
       </c>
       <c r="J54" t="n">
         <v>1542</v>
@@ -8796,7 +8886,7 @@
         <v>6</v>
       </c>
       <c r="P54" t="n">
-        <v>1211</v>
+        <v>1271</v>
       </c>
       <c r="Q54" t="n">
         <v>0.0167</v>
@@ -8946,7 +9036,7 @@
         <v>724</v>
       </c>
       <c r="I57" t="n">
-        <v>1409</v>
+        <v>1481</v>
       </c>
       <c r="J57" t="n">
         <v>1466</v>
@@ -8967,7 +9057,7 @@
         <v>13</v>
       </c>
       <c r="P57" t="n">
-        <v>1404</v>
+        <v>1474</v>
       </c>
       <c r="Q57" t="n">
         <v>0.0195</v>
@@ -9003,7 +9093,7 @@
         <v>764</v>
       </c>
       <c r="I58" t="n">
-        <v>1492</v>
+        <v>1548</v>
       </c>
       <c r="J58" t="n">
         <v>1535</v>
@@ -9024,7 +9114,7 @@
         <v>23</v>
       </c>
       <c r="P58" t="n">
-        <v>1476</v>
+        <v>1520</v>
       </c>
       <c r="Q58" t="n">
         <v>-0.008</v>
@@ -9060,7 +9150,7 @@
         <v>757</v>
       </c>
       <c r="I59" t="n">
-        <v>1370</v>
+        <v>1411</v>
       </c>
       <c r="J59" t="n">
         <v>1535</v>
@@ -9081,7 +9171,7 @@
         <v>3</v>
       </c>
       <c r="P59" t="n">
-        <v>1313</v>
+        <v>1353</v>
       </c>
       <c r="Q59" t="n">
         <v>-0.008</v>
@@ -9117,7 +9207,7 @@
         <v>819</v>
       </c>
       <c r="I60" t="n">
-        <v>1491</v>
+        <v>1521</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -9138,7 +9228,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="n">
-        <v>1428</v>
+        <v>1458</v>
       </c>
       <c r="Q60" t="n">
         <v/>
@@ -9174,7 +9264,7 @@
         <v>947</v>
       </c>
       <c r="I61" t="n">
-        <v>1703</v>
+        <v>1772</v>
       </c>
       <c r="J61" t="n">
         <v>1893</v>
@@ -9195,7 +9285,7 @@
         <v>15</v>
       </c>
       <c r="P61" t="n">
-        <v>1703</v>
+        <v>1771</v>
       </c>
       <c r="Q61" t="n">
         <v>0.09470000000000001</v>
@@ -9231,7 +9321,7 @@
         <v>956</v>
       </c>
       <c r="I62" t="n">
-        <v>1799</v>
+        <v>1863</v>
       </c>
       <c r="J62" t="n">
         <v>1705</v>
@@ -9252,7 +9342,7 @@
         <v>11</v>
       </c>
       <c r="P62" t="n">
-        <v>1730</v>
+        <v>1780</v>
       </c>
       <c r="Q62" t="n">
         <v>-0.0815</v>
@@ -9288,7 +9378,7 @@
         <v>1123</v>
       </c>
       <c r="I63" t="n">
-        <v>1888</v>
+        <v>1945</v>
       </c>
       <c r="J63" t="n">
         <v>1846</v>
@@ -9309,7 +9399,7 @@
         <v>9</v>
       </c>
       <c r="P63" t="n">
-        <v>1789</v>
+        <v>1839</v>
       </c>
       <c r="Q63" t="n">
         <v>0.0109</v>
@@ -9345,7 +9435,7 @@
         <v>1197</v>
       </c>
       <c r="I64" t="n">
-        <v>2049</v>
+        <v>2099</v>
       </c>
       <c r="J64" t="n">
         <v>2150</v>
@@ -9366,7 +9456,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>1981</v>
+        <v>2031</v>
       </c>
       <c r="Q64" t="n">
         <v>0.0149</v>
@@ -9402,7 +9492,7 @@
         <v>1197</v>
       </c>
       <c r="I65" t="n">
-        <v>2346</v>
+        <v>2396</v>
       </c>
       <c r="J65" t="n">
         <v>2150</v>
@@ -9459,7 +9549,7 @@
         <v>1209</v>
       </c>
       <c r="I66" t="n">
-        <v>2027</v>
+        <v>2064</v>
       </c>
       <c r="J66" t="n">
         <v>1920</v>
@@ -9480,7 +9570,7 @@
         <v>8</v>
       </c>
       <c r="P66" t="n">
-        <v>1842</v>
+        <v>1822</v>
       </c>
       <c r="Q66" t="n">
         <v/>
@@ -9516,7 +9606,7 @@
         <v>1444</v>
       </c>
       <c r="I67" t="n">
-        <v>2774</v>
+        <v>2907</v>
       </c>
       <c r="J67" t="n">
         <v>3020</v>
@@ -9537,7 +9627,7 @@
         <v>5</v>
       </c>
       <c r="P67" t="n">
-        <v>2785</v>
+        <v>2947</v>
       </c>
       <c r="Q67" t="n">
         <v>0.0512</v>
@@ -9573,7 +9663,7 @@
         <v>1444</v>
       </c>
       <c r="I68" t="n">
-        <v>2601</v>
+        <v>2351</v>
       </c>
       <c r="J68" t="n">
         <v>3020</v>
@@ -9594,7 +9684,7 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>2601</v>
+        <v>2351</v>
       </c>
       <c r="Q68" t="n">
         <v>0.2878</v>
@@ -9630,7 +9720,7 @@
         <v>624</v>
       </c>
       <c r="I69" t="n">
-        <v>1436</v>
+        <v>1493</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -9651,7 +9741,7 @@
         <v>4</v>
       </c>
       <c r="P69" t="n">
-        <v>1423</v>
+        <v>1485</v>
       </c>
       <c r="Q69" t="n">
         <v/>
@@ -9687,7 +9777,7 @@
         <v>629</v>
       </c>
       <c r="I70" t="n">
-        <v>1502</v>
+        <v>1571</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -9708,7 +9798,7 @@
         <v>3</v>
       </c>
       <c r="P70" t="n">
-        <v>1486</v>
+        <v>1552</v>
       </c>
       <c r="Q70" t="n">
         <v/>
@@ -9744,7 +9834,7 @@
         <v>679</v>
       </c>
       <c r="I71" t="n">
-        <v>1541</v>
+        <v>1599</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -9765,7 +9855,7 @@
         <v>2</v>
       </c>
       <c r="P71" t="n">
-        <v>1500</v>
+        <v>1574</v>
       </c>
       <c r="Q71" t="n">
         <v/>
@@ -9801,7 +9891,7 @@
         <v>687</v>
       </c>
       <c r="I72" t="n">
-        <v>1503</v>
+        <v>1571</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -9822,7 +9912,7 @@
         <v>2</v>
       </c>
       <c r="P72" t="n">
-        <v>1455</v>
+        <v>1552</v>
       </c>
       <c r="Q72" t="n">
         <v/>
@@ -9858,7 +9948,7 @@
         <v>720</v>
       </c>
       <c r="I73" t="n">
-        <v>1643</v>
+        <v>1680</v>
       </c>
       <c r="J73" t="n">
         <v>1775</v>
@@ -9879,7 +9969,7 @@
         <v>21</v>
       </c>
       <c r="P73" t="n">
-        <v>1556</v>
+        <v>1588</v>
       </c>
       <c r="Q73" t="n">
         <v>0.0392</v>
@@ -9915,7 +10005,7 @@
         <v>759</v>
       </c>
       <c r="I74" t="n">
-        <v>1642</v>
+        <v>1700</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -9936,7 +10026,7 @@
         <v>2</v>
       </c>
       <c r="P74" t="n">
-        <v>1622</v>
+        <v>1694</v>
       </c>
       <c r="Q74" t="n">
         <v/>
@@ -9972,7 +10062,7 @@
         <v>760</v>
       </c>
       <c r="I75" t="n">
-        <v>1607</v>
+        <v>1663</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -9993,7 +10083,7 @@
         <v>3</v>
       </c>
       <c r="P75" t="n">
-        <v>1622</v>
+        <v>1694</v>
       </c>
       <c r="Q75" t="n">
         <v/>
@@ -10029,7 +10119,7 @@
         <v>762</v>
       </c>
       <c r="I76" t="n">
-        <v>1706</v>
+        <v>1716</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -10086,7 +10176,7 @@
         <v>769</v>
       </c>
       <c r="I77" t="n">
-        <v>1632</v>
+        <v>1648</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -10143,7 +10233,7 @@
         <v>772</v>
       </c>
       <c r="I78" t="n">
-        <v>1667</v>
+        <v>1732</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -10164,7 +10254,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="n">
-        <v>1654</v>
+        <v>1718</v>
       </c>
       <c r="Q78" t="n">
         <v/>
@@ -10200,7 +10290,7 @@
         <v>824</v>
       </c>
       <c r="I79" t="n">
-        <v>1604</v>
+        <v>1655</v>
       </c>
       <c r="J79" t="n">
         <v>1566</v>
@@ -10221,7 +10311,7 @@
         <v>2</v>
       </c>
       <c r="P79" t="n">
-        <v>1568</v>
+        <v>1616</v>
       </c>
       <c r="Q79" t="n">
         <v/>
@@ -10257,7 +10347,7 @@
         <v>848</v>
       </c>
       <c r="I80" t="n">
-        <v>1722</v>
+        <v>1762</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -10278,7 +10368,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="n">
-        <v>1680</v>
+        <v>1720</v>
       </c>
       <c r="Q80" t="n">
         <v/>
@@ -10314,7 +10404,7 @@
         <v>872</v>
       </c>
       <c r="I81" t="n">
-        <v>1713</v>
+        <v>1776</v>
       </c>
       <c r="J81" t="n">
         <v>1696</v>
@@ -10335,7 +10425,7 @@
         <v>7</v>
       </c>
       <c r="P81" t="n">
-        <v>1685</v>
+        <v>1752</v>
       </c>
       <c r="Q81" t="n">
         <v/>
@@ -10371,7 +10461,7 @@
         <v>985</v>
       </c>
       <c r="I82" t="n">
-        <v>1774</v>
+        <v>1754</v>
       </c>
       <c r="J82" t="n">
         <v>1734</v>
@@ -10392,7 +10482,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="n">
-        <v>1769</v>
+        <v>1799</v>
       </c>
       <c r="Q82" t="n">
         <v/>
@@ -10428,7 +10518,7 @@
         <v>1024</v>
       </c>
       <c r="I83" t="n">
-        <v>1988</v>
+        <v>2076</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -10449,7 +10539,7 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>1988</v>
+        <v>2076</v>
       </c>
       <c r="Q83" t="n">
         <v/>
@@ -10485,7 +10575,7 @@
         <v>779</v>
       </c>
       <c r="I84" t="n">
-        <v>1769</v>
+        <v>1814</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -10506,7 +10596,7 @@
         <v>2</v>
       </c>
       <c r="P84" t="n">
-        <v>1806</v>
+        <v>1836</v>
       </c>
       <c r="Q84" t="n">
         <v/>
@@ -10542,7 +10632,7 @@
         <v>931</v>
       </c>
       <c r="I85" t="n">
-        <v>1912</v>
+        <v>1990</v>
       </c>
       <c r="J85" t="n">
         <v>1855</v>
@@ -10563,7 +10653,7 @@
         <v>4</v>
       </c>
       <c r="P85" t="n">
-        <v>1915</v>
+        <v>1981</v>
       </c>
       <c r="Q85" t="n">
         <v>0.0183</v>
@@ -10599,7 +10689,7 @@
         <v>969</v>
       </c>
       <c r="I86" t="n">
-        <v>1734</v>
+        <v>1757</v>
       </c>
       <c r="J86" t="n">
         <v>1714</v>
@@ -10620,7 +10710,7 @@
         <v>11</v>
       </c>
       <c r="P86" t="n">
-        <v>1734</v>
+        <v>1790</v>
       </c>
       <c r="Q86" t="n">
         <v>-0.0061</v>
@@ -10656,7 +10746,7 @@
         <v>1017</v>
       </c>
       <c r="I87" t="n">
-        <v>2003</v>
+        <v>2081</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -10677,7 +10767,7 @@
         <v>4</v>
       </c>
       <c r="P87" t="n">
-        <v>1943</v>
+        <v>2088</v>
       </c>
       <c r="Q87" t="n">
         <v/>
@@ -10713,7 +10803,7 @@
         <v>1076</v>
       </c>
       <c r="I88" t="n">
-        <v>2146</v>
+        <v>2193</v>
       </c>
       <c r="J88" t="n">
         <v>2125</v>
@@ -10734,7 +10824,7 @@
         <v>7</v>
       </c>
       <c r="P88" t="n">
-        <v>2086</v>
+        <v>2121</v>
       </c>
       <c r="Q88" t="n">
         <v/>
@@ -10770,7 +10860,7 @@
         <v>1093</v>
       </c>
       <c r="I89" t="n">
-        <v>1955</v>
+        <v>2059</v>
       </c>
       <c r="J89" t="n">
         <v>1900</v>
@@ -10791,7 +10881,7 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>1955</v>
+        <v>2059</v>
       </c>
       <c r="Q89" t="n">
         <v>-0.101</v>
@@ -10827,7 +10917,7 @@
         <v>1171</v>
       </c>
       <c r="I90" t="n">
-        <v>2059</v>
+        <v>2105</v>
       </c>
       <c r="J90" t="n">
         <v>2064</v>
@@ -10848,7 +10938,7 @@
         <v>13</v>
       </c>
       <c r="P90" t="n">
-        <v>2005</v>
+        <v>2052</v>
       </c>
       <c r="Q90" t="n">
         <v>-0.0183</v>
@@ -10884,7 +10974,7 @@
         <v>1198</v>
       </c>
       <c r="I91" t="n">
-        <v>2441</v>
+        <v>2519</v>
       </c>
       <c r="J91" t="n">
         <v>2282</v>
@@ -10905,7 +10995,7 @@
         <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>2356</v>
+        <v>2439</v>
       </c>
       <c r="Q91" t="n">
         <v/>
@@ -10941,7 +11031,7 @@
         <v>1210</v>
       </c>
       <c r="I92" t="n">
-        <v>2264</v>
+        <v>2309</v>
       </c>
       <c r="J92" t="n">
         <v>2193</v>
@@ -10962,7 +11052,7 @@
         <v>7</v>
       </c>
       <c r="P92" t="n">
-        <v>2280</v>
+        <v>2385</v>
       </c>
       <c r="Q92" t="n">
         <v/>
@@ -10998,7 +11088,7 @@
         <v>1253</v>
       </c>
       <c r="I93" t="n">
-        <v>2396</v>
+        <v>2437</v>
       </c>
       <c r="J93" t="n">
         <v>2237</v>
@@ -11019,7 +11109,7 @@
         <v>5</v>
       </c>
       <c r="P93" t="n">
-        <v>2285</v>
+        <v>2320</v>
       </c>
       <c r="Q93" t="n">
         <v>-0.076</v>
@@ -11055,7 +11145,7 @@
         <v>1253</v>
       </c>
       <c r="I94" t="n">
-        <v>2307</v>
+        <v>2443</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -11112,7 +11202,7 @@
         <v>1489</v>
       </c>
       <c r="I95" t="n">
-        <v>2873</v>
+        <v>2957</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -11133,7 +11223,7 @@
         <v>3</v>
       </c>
       <c r="P95" t="n">
-        <v>2842</v>
+        <v>2962</v>
       </c>
       <c r="Q95" t="n">
         <v/>
@@ -11169,7 +11259,7 @@
         <v>1709</v>
       </c>
       <c r="I96" t="n">
-        <v>3338</v>
+        <v>3414</v>
       </c>
       <c r="J96" t="n">
         <v>3349</v>
@@ -11190,7 +11280,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="n">
-        <v>3370</v>
+        <v>3432</v>
       </c>
       <c r="Q96" t="n">
         <v/>

--- a/output/Morgan_Recap_Data_Tape.xlsx
+++ b/output/Morgan_Recap_Data_Tape.xlsx
@@ -959,75 +959,80 @@
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>Built</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="H16" s="18" t="inlineStr">
         <is>
           <t>$/Unit</t>
         </is>
       </c>
-      <c r="H16" s="18" t="inlineStr">
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>Occ</t>
         </is>
       </c>
-      <c r="I16" s="18" t="inlineStr">
+      <c r="J16" s="18" t="inlineStr">
         <is>
           <t>Contract /mo</t>
         </is>
       </c>
-      <c r="J16" s="18" t="inlineStr">
+      <c r="K16" s="18" t="inlineStr">
         <is>
           <t>New T/O</t>
         </is>
       </c>
-      <c r="K16" s="18" t="inlineStr">
+      <c r="L16" s="18" t="inlineStr">
         <is>
           <t>T12 NOI</t>
         </is>
       </c>
-      <c r="L16" s="18" t="inlineStr">
+      <c r="M16" s="18" t="inlineStr">
         <is>
           <t>Act Cap</t>
         </is>
       </c>
-      <c r="M16" s="18" t="inlineStr">
+      <c r="N16" s="18" t="inlineStr">
         <is>
           <t>JLL UW Cap</t>
         </is>
       </c>
-      <c r="N16" s="18" t="inlineStr">
+      <c r="O16" s="18" t="inlineStr">
         <is>
           <t>Yr-1 Cap</t>
         </is>
       </c>
-      <c r="O16" s="18" t="inlineStr">
+      <c r="P16" s="18" t="inlineStr">
         <is>
           <t>Exit Cap</t>
         </is>
       </c>
-      <c r="P16" s="18" t="inlineStr">
+      <c r="Q16" s="18" t="inlineStr">
         <is>
           <t>JLL UW LIRR</t>
         </is>
       </c>
-      <c r="Q16" s="18" t="inlineStr">
+      <c r="R16" s="18" t="inlineStr">
         <is>
           <t>EM</t>
         </is>
       </c>
-      <c r="R16" s="17" t="inlineStr">
+      <c r="S16" s="17" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -1041,46 +1046,51 @@
       </c>
       <c r="B17" s="20" t="n"/>
       <c r="C17" s="20" t="n"/>
-      <c r="D17" s="21" t="n">
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>Houston, TX</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="n">
         <v>459</v>
       </c>
-      <c r="E17" s="22" t="n">
+      <c r="F17" s="22" t="n">
         <v>2015</v>
       </c>
-      <c r="F17" s="23" t="n">
+      <c r="G17" s="23" t="n">
         <v>127000000</v>
       </c>
-      <c r="G17" s="24" t="n">
+      <c r="H17" s="24" t="n">
         <v>276688.4531590414</v>
       </c>
-      <c r="H17" s="25" t="n">
+      <c r="I17" s="25" t="n">
         <v>0.9694989106753813</v>
       </c>
-      <c r="I17" s="24" t="n">
+      <c r="J17" s="24" t="n">
         <v>2330.481481481481</v>
       </c>
-      <c r="J17" s="25" t="n">
+      <c r="K17" s="25" t="n">
         <v>0.03463420147578833</v>
       </c>
-      <c r="K17" s="23" t="n">
+      <c r="L17" s="23" t="n">
         <v>6556237</v>
       </c>
-      <c r="L17" s="26" t="n">
+      <c r="M17" s="26" t="n">
         <v>0.05162391338582677</v>
       </c>
-      <c r="M17" s="26" t="n">
+      <c r="N17" s="26" t="n">
         <v>0.05070069856746456</v>
       </c>
-      <c r="N17" s="26" t="n">
+      <c r="O17" s="26" t="n">
         <v>0.05335014871664925</v>
       </c>
-      <c r="O17" s="26" t="n">
+      <c r="P17" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="P17" s="25" t="n">
+      <c r="Q17" s="25" t="n">
         <v>0.1629796862069719</v>
       </c>
-      <c r="Q17" s="27" t="n">
+      <c r="R17" s="27" t="n">
         <v>1.999137963456238</v>
       </c>
     </row>
@@ -1092,46 +1102,51 @@
       </c>
       <c r="B18" s="29" t="n"/>
       <c r="C18" s="29" t="n"/>
-      <c r="D18" s="30" t="n">
+      <c r="D18" s="30" t="inlineStr">
+        <is>
+          <t>Miami, FL</t>
+        </is>
+      </c>
+      <c r="E18" s="30" t="n">
         <v>236</v>
       </c>
-      <c r="E18" s="31" t="n">
+      <c r="F18" s="31" t="n">
         <v>2024</v>
       </c>
-      <c r="F18" s="32" t="n">
+      <c r="G18" s="32" t="n">
         <v>85000000</v>
       </c>
-      <c r="G18" s="33" t="n">
+      <c r="H18" s="33" t="n">
         <v>360169.4915254237</v>
       </c>
-      <c r="H18" s="34" t="n">
+      <c r="I18" s="34" t="n">
         <v>0.923728813559322</v>
       </c>
-      <c r="I18" s="33" t="n">
+      <c r="J18" s="33" t="n">
         <v>2528.881355932203</v>
       </c>
-      <c r="J18" s="34" t="n">
+      <c r="K18" s="34" t="n">
         <v>-0.115485050906139</v>
       </c>
-      <c r="K18" s="32" t="n">
+      <c r="L18" s="32" t="n">
         <v>3802396</v>
       </c>
-      <c r="L18" s="35" t="n">
+      <c r="M18" s="35" t="n">
         <v>0.04473407058823529</v>
       </c>
-      <c r="M18" s="35" t="n">
+      <c r="N18" s="35" t="n">
         <v>0.04666074939670589</v>
       </c>
-      <c r="N18" s="35" t="n">
+      <c r="O18" s="35" t="n">
         <v>0.0479255411819897</v>
       </c>
-      <c r="O18" s="35" t="n">
+      <c r="P18" s="35" t="n">
         <v>0.0475</v>
       </c>
-      <c r="P18" s="34" t="n">
+      <c r="Q18" s="34" t="n">
         <v>0.1515156658203647</v>
       </c>
-      <c r="Q18" s="36" t="n">
+      <c r="R18" s="36" t="n">
         <v>1.922478917528772</v>
       </c>
     </row>
@@ -1143,46 +1158,51 @@
       </c>
       <c r="B19" s="20" t="n"/>
       <c r="C19" s="20" t="n"/>
-      <c r="D19" s="21" t="n">
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>Houston, TX</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="n">
         <v>322</v>
       </c>
-      <c r="E19" s="22" t="n">
+      <c r="F19" s="22" t="n">
         <v>2016</v>
       </c>
-      <c r="F19" s="23" t="n">
+      <c r="G19" s="23" t="n">
         <v>60000000</v>
       </c>
-      <c r="G19" s="24" t="n">
+      <c r="H19" s="24" t="n">
         <v>186335.4037267081</v>
       </c>
-      <c r="H19" s="25" t="n">
+      <c r="I19" s="25" t="n">
         <v>0.937888198757764</v>
       </c>
-      <c r="I19" s="24" t="n">
+      <c r="J19" s="24" t="n">
         <v>1687.074534161491</v>
       </c>
-      <c r="J19" s="25" t="n">
+      <c r="K19" s="25" t="n">
         <v>-0.1521936575618804</v>
       </c>
-      <c r="K19" s="23" t="n">
+      <c r="L19" s="23" t="n">
         <v>2772820</v>
       </c>
-      <c r="L19" s="26" t="n">
+      <c r="M19" s="26" t="n">
         <v>0.04621366666666667</v>
       </c>
-      <c r="M19" s="26" t="n">
+      <c r="N19" s="26" t="n">
         <v>0.051301136661004</v>
       </c>
-      <c r="N19" s="26" t="n">
+      <c r="O19" s="26" t="n">
         <v>0.05396175469133623</v>
       </c>
-      <c r="O19" s="26" t="n">
+      <c r="P19" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="P19" s="25" t="n">
+      <c r="Q19" s="25" t="n">
         <v>0.1766852207761906</v>
       </c>
-      <c r="Q19" s="27" t="n">
+      <c r="R19" s="27" t="n">
         <v>2.144502169992451</v>
       </c>
     </row>
@@ -1194,46 +1214,51 @@
       </c>
       <c r="B20" s="29" t="n"/>
       <c r="C20" s="29" t="n"/>
-      <c r="D20" s="30" t="n">
+      <c r="D20" s="30" t="inlineStr">
+        <is>
+          <t>Houston, TX</t>
+        </is>
+      </c>
+      <c r="E20" s="30" t="n">
         <v>215</v>
       </c>
-      <c r="E20" s="31" t="n">
+      <c r="F20" s="31" t="n">
         <v>2015</v>
       </c>
-      <c r="F20" s="32" t="n">
+      <c r="G20" s="32" t="n">
         <v>46500000</v>
       </c>
-      <c r="G20" s="33" t="n">
+      <c r="H20" s="33" t="n">
         <v>216279.0697674419</v>
       </c>
-      <c r="H20" s="34" t="n">
+      <c r="I20" s="34" t="n">
         <v>0.9488372093023256</v>
       </c>
-      <c r="I20" s="33" t="n">
+      <c r="J20" s="33" t="n">
         <v>1940.772093023256</v>
       </c>
-      <c r="J20" s="34" t="n">
+      <c r="K20" s="34" t="n">
         <v>-0.07013679161485165</v>
       </c>
-      <c r="K20" s="32" t="n">
+      <c r="L20" s="32" t="n">
         <v>2240292</v>
       </c>
-      <c r="L20" s="35" t="n">
+      <c r="M20" s="35" t="n">
         <v>0.04817832258064516</v>
       </c>
-      <c r="M20" s="35" t="n">
+      <c r="N20" s="35" t="n">
         <v>0.04974305591528602</v>
       </c>
-      <c r="N20" s="35" t="n">
+      <c r="O20" s="35" t="n">
         <v>0.05298602966198496</v>
       </c>
-      <c r="O20" s="35" t="n">
+      <c r="P20" s="35" t="n">
         <v>0.05</v>
       </c>
-      <c r="P20" s="34" t="n">
+      <c r="Q20" s="34" t="n">
         <v>0.1638007066406761</v>
       </c>
-      <c r="Q20" s="36" t="n">
+      <c r="R20" s="36" t="n">
         <v>2.024875332077828</v>
       </c>
     </row>
@@ -1245,36 +1270,41 @@
       </c>
       <c r="B21" s="20" t="n"/>
       <c r="C21" s="20" t="n"/>
-      <c r="D21" s="21" t="n">
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>3 Houston · 1 Miami</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="n">
         <v>1232</v>
       </c>
-      <c r="E21" s="22" t="inlineStr"/>
-      <c r="F21" s="23" t="n">
+      <c r="F21" s="22" t="inlineStr"/>
+      <c r="G21" s="23" t="n">
         <v>318500000</v>
       </c>
-      <c r="G21" s="24" t="n">
+      <c r="H21" s="24" t="n">
         <v>258522.7272727273</v>
       </c>
-      <c r="H21" s="25" t="n">
+      <c r="I21" s="25" t="n">
         <v>0.9488636363636364</v>
       </c>
-      <c r="I21" s="24" t="inlineStr"/>
-      <c r="J21" s="25" t="inlineStr"/>
-      <c r="K21" s="23" t="n">
+      <c r="J21" s="24" t="inlineStr"/>
+      <c r="K21" s="25" t="inlineStr"/>
+      <c r="L21" s="23" t="n">
         <v>15371745</v>
       </c>
-      <c r="L21" s="26" t="n">
+      <c r="M21" s="26" t="n">
         <v>0.04826293563579278</v>
       </c>
-      <c r="M21" s="26" t="n">
+      <c r="N21" s="26" t="n">
         <v>0.04959583270489495</v>
       </c>
-      <c r="N21" s="26" t="inlineStr"/>
-      <c r="O21" s="26" t="n">
+      <c r="O21" s="26" t="inlineStr"/>
+      <c r="P21" s="26" t="n">
         <v>0.04934595209550115</v>
       </c>
-      <c r="P21" s="25" t="inlineStr"/>
-      <c r="Q21" s="27" t="inlineStr"/>
+      <c r="Q21" s="25" t="inlineStr"/>
+      <c r="R21" s="27" t="inlineStr"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
@@ -1879,12 +1909,12 @@
   </sheetData>
   <mergeCells count="62">
     <mergeCell ref="A13:W13"/>
-    <mergeCell ref="R16:W16"/>
     <mergeCell ref="E10:G10"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="N28:W28"/>
     <mergeCell ref="M10:O10"/>
     <mergeCell ref="D37:V37"/>
+    <mergeCell ref="S16:W16"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="Q10:S10"/>
     <mergeCell ref="A18:C18"/>
